--- a/data/dashboard-new.xlsx
+++ b/data/dashboard-new.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H108"/>
   <cols>
     <col min="1" max="1" width="25.83203125" customWidth="1"/>
     <col min="2" max="2" width="35.83203125" customWidth="1"/>
@@ -437,64 +437,2819 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>group</v>
+        <v>[CUST] Управление клиентами</v>
       </c>
       <c r="B2" t="str">
-        <v>base</v>
+        <v>Персональные менеджеры</v>
       </c>
       <c r="C2" t="str">
-        <v>key</v>
+        <v>Закрепление/открепление/изменение Личного Оператора</v>
       </c>
       <c r="D2" t="str">
-        <v>2.5 [FINAL] Я как клиент хочу перейти на тарифный план UP в мобильном приложении</v>
-      </c>
-      <c r="E2">
-        <v>130</v>
-      </c>
-      <c r="F2">
-        <v>25</v>
-      </c>
-      <c r="G2">
-        <v>16</v>
-      </c>
-      <c r="H2">
-        <v>15</v>
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>group</v>
+        <v>[CUST] Управление клиентами</v>
       </c>
       <c r="B3" t="str">
-        <v>base</v>
+        <v>Создание(изменение) Группы Компании/Добавление Компании в ГК</v>
       </c>
       <c r="C3" t="str">
-        <v>key</v>
+        <v/>
       </c>
       <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>[CUST] Управление клиентами</v>
+      </c>
+      <c r="B4" t="str">
+        <v>[GOVERNANCE] Работа с государственными клиентами</v>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>[SALE] Продажи</v>
+      </c>
+      <c r="B5" t="str">
+        <v>[CONNECT] Продажа услуг связи</v>
+      </c>
+      <c r="C5" t="str">
+        <v>[SIM] Я, как клиент, покупаю SIM новую карту</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>[SALE] Продажи</v>
+      </c>
+      <c r="B6" t="str">
+        <v>[CONNECT] Продажа услуг связи</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Я, как клиент покупаю новую сим-карту с красивым номером</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>[SALE] Продажи</v>
+      </c>
+      <c r="B7" t="str">
+        <v>[CONNECT] Продажа услуг связи</v>
+      </c>
+      <c r="C7" t="str">
+        <v>[NUMBER] Я, как клиент, хочу купить красивый номер на существующую СИМ карту</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>[SALE] Продажи</v>
+      </c>
+      <c r="B8" t="str">
+        <v>[CONNECT] Продажа услуг связи</v>
+      </c>
+      <c r="C8" t="str">
+        <v>[ESIM] Я, как клиент, хочу купить eSIM</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>[SALE] Продажи</v>
+      </c>
+      <c r="B9" t="str">
+        <v>[CONNECT] Продажа услуг связи</v>
+      </c>
+      <c r="C9" t="str">
+        <v>[MNP] Я, как клиент, хочу перейти в билайн с сохранением номера</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>[SALE] Продажи</v>
+      </c>
+      <c r="B10" t="str">
+        <v>[CONNECT] Продажа услуг связи</v>
+      </c>
+      <c r="C10" t="str">
+        <v>[FIX] Я, как клиент, хочу купить домашний интернет и ТВ</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>[SALE] Продажи</v>
+      </c>
+      <c r="B11" t="str">
+        <v>[CONNECT] Продажа услуг связи</v>
+      </c>
+      <c r="C11" t="str">
+        <v>[RESTORE] Я, как клиент, хочу восстановить свой номер телефона и купить мобильную связь билайн</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>[SALE] Продажи</v>
+      </c>
+      <c r="B12" t="str">
+        <v>[CONVERGENT] Продажа конвергентных продуктов</v>
+      </c>
+      <c r="C12" t="str">
+        <v>[NEWSIM] Я, как клиент, хочу подключить домашний интернет, ТВ билайн и купить новую SIM</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>[SALE] Продажи</v>
+      </c>
+      <c r="B13" t="str">
+        <v>[CONVERGENT] Продажа конвергентных продуктов</v>
+      </c>
+      <c r="C13" t="str">
+        <v>[PACKAGE] Я, как клиент, хочу подключить домашний интернет, ТВ билайн и сменить тариф на существующем номере</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>[SALE] Продажи</v>
+      </c>
+      <c r="B14" t="str">
+        <v>[CONVERGENT] Продажа конвергентных продуктов</v>
+      </c>
+      <c r="C14" t="str">
+        <v>[NEWESIM] Я, как клиент, хочу подключить домашний интернет, ТВ билайн и и купить eSIM</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>[SALE] Продажи</v>
+      </c>
+      <c r="B15" t="str">
+        <v>[CONVERGENT] Продажа конвергентных продуктов</v>
+      </c>
+      <c r="C15" t="str">
+        <v>[MNP] Я, как клиент, хочу подключить домашний интернет, ТВ билайн и перейти по MNP с сохранением своего номера</v>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>[SALE] Продажи</v>
+      </c>
+      <c r="B16" t="str">
+        <v>[CTE] Продажа и аренда фикс.оборудования</v>
+      </c>
+      <c r="C16" t="str">
+        <v>[SALE] Я, как клиент, хочу купить обрудования для домашнего интернета и ТВ</v>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>[SALE] Продажи</v>
+      </c>
+      <c r="B17" t="str">
+        <v>[CTE] Продажа и аренда фикс.оборудования</v>
+      </c>
+      <c r="C17" t="str">
+        <v>[RENT] Я, как клиент, хочу взять в аренту оборудование для домашнего интернета и ТВ</v>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>[SALE] Продажи</v>
+      </c>
+      <c r="B18" t="str">
+        <v>[CTE] Продажа и аренда фикс.оборудования</v>
+      </c>
+      <c r="C18" t="str">
+        <v>[RETURNS] Я, как клиент, врзвращаю оборудование</v>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>[SALE] Продажи</v>
+      </c>
+      <c r="B19" t="str">
+        <v>[RETAIL] Розничные продажи</v>
+      </c>
+      <c r="C19" t="str">
+        <v>[GOODS] Я, как клиент, хочу купить товар</v>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>[SALE] Продажи</v>
+      </c>
+      <c r="B20" t="str">
+        <v>[RETAIL] Розничные продажи</v>
+      </c>
+      <c r="C20" t="str">
+        <v>[TRADEIN] Я, как клиент, хочу купить товар в trade-in</v>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>[SALE] Продажи</v>
+      </c>
+      <c r="B21" t="str">
+        <v>[RETAIL] Розничные продажи</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Я, как клиент, хочу купить товар в интернет-магазине</v>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>[SALE] Продажи</v>
+      </c>
+      <c r="B22" t="str">
+        <v>[RETAIL] Розничные продажи</v>
+      </c>
+      <c r="C22" t="str">
+        <v>[DIGITAL] Я, как клиент, хочу купить цифровой продукт</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>[SALE] Продажи</v>
+      </c>
+      <c r="B23" t="str">
+        <v>[RETAIL] Розничные продажи</v>
+      </c>
+      <c r="C23" t="str">
+        <v>[RETURNS] Я, как клиент, хочу сделать возврат товара</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>[SALE] Продажи</v>
+      </c>
+      <c r="B24" t="str">
+        <v>[RETAIL] Розничные продажи</v>
+      </c>
+      <c r="C24" t="str">
+        <v>[CANCEL] Я, как клиент, отменяю заказ</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>[SALE] Продажи</v>
+      </c>
+      <c r="B25" t="str">
+        <v>[PLAY] Игры и развлечения</v>
+      </c>
+      <c r="C25" t="str">
+        <v>[BOOKS] Я, как клиент, хочу купить подписку на билайн книги</v>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>[SALE] Продажи</v>
+      </c>
+      <c r="B26" t="str">
+        <v>[PLAY] Игры и развлечения</v>
+      </c>
+      <c r="C26" t="str">
+        <v>[CLOUD] Я, как клиент, хочу купить подписку на облако билайн</v>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>[AGREEMENT] Управление контрактами и условиями договоров</v>
+      </c>
+      <c r="B27" t="str">
+        <v>[PRIVATE] Предоставление непубличных условий клиентам mob</v>
+      </c>
+      <c r="C27" t="str">
+        <v>ТБД</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>[AGREEMENT] Управление контрактами и условиями договоров</v>
+      </c>
+      <c r="B28" t="str">
+        <v>ТБД Сохранение/расторжение Клиента</v>
+      </c>
+      <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>[AGREEMENT] Управление контрактами и условиями договоров</v>
+      </c>
+      <c r="B29" t="str">
+        <v>[ARCHIVE] Архивация клиентской документации</v>
+      </c>
+      <c r="C29" t="str">
+        <v/>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>[AGREEMENT] Управление контрактами и условиями договоров</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Работа с нерезидентами</v>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>[AGREEMENT] Управление контрактами и условиями договоров</v>
+      </c>
+      <c r="B31" t="str">
+        <v>[SLA] Предоставление уровня обслуживания (АТ,SM в том числе)</v>
+      </c>
+      <c r="C31" t="str">
+        <v/>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>[USE] Предоставление и тарификация услуг</v>
+      </c>
+      <c r="B32" t="str">
+        <v>[CONNECT] Предоставление услуг связи</v>
+      </c>
+      <c r="C32" t="str">
+        <v>[VOICE] Я, как клиент, хочу сделать голосовой звонок</v>
+      </c>
+      <c r="D32" t="str">
+        <v/>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>[USE] Предоставление и тарификация услуг</v>
+      </c>
+      <c r="B33" t="str">
+        <v>[CONNECT] Предоставление услуг связи</v>
+      </c>
+      <c r="C33" t="str">
+        <v>[SMS] Я, как клиент, хочу послать SMS</v>
+      </c>
+      <c r="D33" t="str">
+        <v/>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>[USE] Предоставление и тарификация услуг</v>
+      </c>
+      <c r="B34" t="str">
+        <v>[CONNECT] Предоставление услуг связи</v>
+      </c>
+      <c r="C34" t="str">
+        <v>[INETMOBILE] Я, как клиент, хочу воспользоваться мобильным интернетом</v>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>[USE] Предоставление и тарификация услуг</v>
+      </c>
+      <c r="B35" t="str">
+        <v>[CONNECT] Предоставление услуг связи</v>
+      </c>
+      <c r="C35" t="str">
+        <v>[INETFIX] Я, как клиент, хочу воспользоваться домашним интернетом</v>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>[USE] Предоставление и тарификация услуг</v>
+      </c>
+      <c r="B36" t="str">
+        <v>[VAS] Предоставление услуг VAS платформ</v>
+      </c>
+      <c r="C36" t="str">
+        <v>[TV] Я, как клиент, хочу посмотреть TV</v>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>[USE] Предоставление и тарификация услуг</v>
+      </c>
+      <c r="B37" t="str">
+        <v>[VAS] Предоставление услуг VAS платформ</v>
+      </c>
+      <c r="C37" t="str">
+        <v>[MOVIE] Я, как клиент, хочу посмотреть фильм на билайн ТВ</v>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>[USE] Предоставление и тарификация услуг</v>
+      </c>
+      <c r="B38" t="str">
+        <v>[VAS] Предоставление услуг VAS платформ</v>
+      </c>
+      <c r="C38" t="str">
+        <v>[BOOKS] Я, как клиент, хочу почитать книги билайн</v>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>[USE] Предоставление и тарификация услуг</v>
+      </c>
+      <c r="B39" t="str">
+        <v>[VAS] Предоставление услуг VAS платформ</v>
+      </c>
+      <c r="C39" t="str">
+        <v>[CLOUD] Я, как клиент, хоочу воспользоваться облаком билайн</v>
+      </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>[SUPPORT] Обслуживание</v>
+      </c>
+      <c r="B40" t="str">
+        <v>[TARIF] Смена тарифного плана</v>
+      </c>
+      <c r="C40" t="str">
+        <v>[MOBILE] Я, как клиент, хочу сменить мобильный тарифный план</v>
+      </c>
+      <c r="D40" t="str">
+        <v>2.5 [FINAL] Я как клиент хочу перейти на тарифный план UP в мобильном приложении</v>
+      </c>
+      <c r="E40">
+        <v>130</v>
+      </c>
+      <c r="F40">
+        <v>25</v>
+      </c>
+      <c r="G40">
+        <v>16</v>
+      </c>
+      <c r="H40">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>[SUPPORT] Обслуживание</v>
+      </c>
+      <c r="B41" t="str">
+        <v>[TARIF] Смена тарифного плана</v>
+      </c>
+      <c r="C41" t="str">
+        <v>[MOBILE] Я, как клиент, хочу сменить мобильный тарифный план</v>
+      </c>
+      <c r="D41" t="str">
         <v>2.1 Я как клиент перехожу на Тарифны План Up в личном кабинете на сайте</v>
       </c>
-      <c r="E3">
+      <c r="E41">
         <v>260</v>
       </c>
-      <c r="F3">
+      <c r="F41">
         <v>119</v>
       </c>
-      <c r="G3">
+      <c r="G41">
         <v>15</v>
       </c>
-      <c r="H3">
+      <c r="H41">
         <v>13</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>[SUPPORT] Обслуживание</v>
+      </c>
+      <c r="B42" t="str">
+        <v>[TARIF] Смена тарифного плана</v>
+      </c>
+      <c r="C42" t="str">
+        <v>[FIX] Я, как клиент, хочу сменить тарифный план на домашний интернет и ТВ</v>
+      </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>[SUPPORT] Обслуживание</v>
+      </c>
+      <c r="B43" t="str">
+        <v>[TARIF] Смена тарифного плана</v>
+      </c>
+      <c r="C43" t="str">
+        <v>[CONVERGENT] Я, как клиент, хочу поменять условия конвергентного тарифного плана</v>
+      </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>[SUPPORT] Обслуживание</v>
+      </c>
+      <c r="B44" t="str">
+        <v>[SERVICE] Подключение/отключение услуг</v>
+      </c>
+      <c r="C44" t="str">
+        <v>[MOBILE] Я, как клиент, хочу подключить или отключить услугу на мобильном тарифном плане</v>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>[SUPPORT] Обслуживание</v>
+      </c>
+      <c r="B45" t="str">
+        <v>[SERVICE] Подключение/отключение услуг</v>
+      </c>
+      <c r="C45" t="str">
+        <v>[FIX] Я, как клиент, хочу подключить или отключить услугу фиксированной связи</v>
+      </c>
+      <c r="D45" t="str">
+        <v/>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>[SUPPORT] Обслуживание</v>
+      </c>
+      <c r="B46" t="str">
+        <v>[SERVICE] Подключение/отключение услуг</v>
+      </c>
+      <c r="C46" t="str">
+        <v>[CONVERGENT] Я, как клиент, хочу поменять условия конвергентного тарифного плана</v>
+      </c>
+      <c r="D46" t="str">
+        <v/>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>[SUPPORT] Обслуживание</v>
+      </c>
+      <c r="B47" t="str">
+        <v>[FAMALY] Семья в билайн</v>
+      </c>
+      <c r="C47" t="str">
+        <v>[SUBSCRIBE] Я, как клиент, хочу подключить подписку Все для семьи</v>
+      </c>
+      <c r="D47" t="str">
+        <v/>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>[SUPPORT] Обслуживание</v>
+      </c>
+      <c r="B48" t="str">
+        <v>[FAMALY] Семья в билайн</v>
+      </c>
+      <c r="C48" t="str">
+        <v>[INCLUDE] Я, как клиент, хоче подключить близких в в Семью билайн</v>
+      </c>
+      <c r="D48" t="str">
+        <v/>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>[SUPPORT] Обслуживание</v>
+      </c>
+      <c r="B49" t="str">
+        <v>[FAMALY] Семья в билайн</v>
+      </c>
+      <c r="C49" t="str">
+        <v>[SHARE] Я, как клиент, хочу поделиться тарифом с близкими</v>
+      </c>
+      <c r="D49" t="str">
+        <v/>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>[SUPPORT] Обслуживание</v>
+      </c>
+      <c r="B50" t="str">
+        <v>[FAMALY] Семья в билайн</v>
+      </c>
+      <c r="C50" t="str">
+        <v>[INFO] Я, как клиент, хочу получить информацию о балансах близких</v>
+      </c>
+      <c r="D50" t="str">
+        <v/>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>[SUPPORT] Обслуживание</v>
+      </c>
+      <c r="B51" t="str">
+        <v>[ACCOUNT] Управление аккаунтами</v>
+      </c>
+      <c r="C51" t="str">
+        <v>[ELK] Я, как клиент, хочу добавить аккаунт для управления в ЕЛК</v>
+      </c>
+      <c r="D51" t="str">
+        <v/>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>[SUPPORT] Обслуживание</v>
+      </c>
+      <c r="B52" t="str">
+        <v>[ACCOUNT] Управление аккаунтами</v>
+      </c>
+      <c r="C52" t="str">
+        <v>[APP] Я, как клиент, хчоу добавить аккаунт для управления в мобильном приложении</v>
+      </c>
+      <c r="D52" t="str">
+        <v/>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+      <c r="H52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>[SUPPORT] Обслуживание</v>
+      </c>
+      <c r="B53" t="str">
+        <v>[DEVICE] Замена SIM и номера</v>
+      </c>
+      <c r="C53" t="str">
+        <v>[MSISDN] Я,  как клиент, хочу поменять номер телефона</v>
+      </c>
+      <c r="D53" t="str">
+        <v/>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>[SUPPORT] Обслуживание</v>
+      </c>
+      <c r="B54" t="str">
+        <v>[DEVICE] Замена SIM и номера</v>
+      </c>
+      <c r="C54" t="str">
+        <v>[SIM] Я,  как  клиент, хочу поменять SIM карту</v>
+      </c>
+      <c r="D54" t="str">
+        <v/>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>[SUPPORT] Обслуживание</v>
+      </c>
+      <c r="B55" t="str">
+        <v>[INFO] Изменение/подтверждение персональных данных</v>
+      </c>
+      <c r="C55" t="str">
+        <v>[ESIA] Я, как клиент, хочу обновить персональные данные через ГОСУСЛУГИ</v>
+      </c>
+      <c r="D55" t="str">
+        <v/>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>[SUPPORT] Обслуживание</v>
+      </c>
+      <c r="B56" t="str">
+        <v>[INFO] Изменение/подтверждение персональных данных</v>
+      </c>
+      <c r="C56" t="str">
+        <v>[OFFICE] Я, как клиент, хочу обновить персональные данные в офисе билайн</v>
+      </c>
+      <c r="D56" t="str">
+        <v/>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>[SUPPORT] Обслуживание</v>
+      </c>
+      <c r="B57" t="str">
+        <v>[INFO] Изменение/подтверждение персональных данных</v>
+      </c>
+      <c r="C57" t="str">
+        <v>[CONTRACT] я, как клиент изменяю данные по договору/клиенту (изменение ИНН, наименования, КПП, адреса, контактного лица и прочее)</v>
+      </c>
+      <c r="D57" t="str">
+        <v/>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>[SUPPORT] Обслуживание</v>
+      </c>
+      <c r="B58" t="str">
+        <v>[OWNER] Смена владельца номера</v>
+      </c>
+      <c r="C58" t="str">
+        <v>[INDIVIDUAL] Я, как клиент, хочу переормить мобильный номер другого человека на себя</v>
+      </c>
+      <c r="D58" t="str">
+        <v/>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>[SUPPORT] Обслуживание</v>
+      </c>
+      <c r="B59" t="str">
+        <v>[OWNER] Смена владельца номера</v>
+      </c>
+      <c r="C59" t="str">
+        <v>[IDENTIFY] Я, как клиент, хочу переформить мобильный номер на себя с альтернативной идентификацией</v>
+      </c>
+      <c r="D59" t="str">
+        <v/>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>[SUPPORT] Обслуживание</v>
+      </c>
+      <c r="B60" t="str">
+        <v>[OWNER] Смена владельца номера</v>
+      </c>
+      <c r="C60" t="str">
+        <v>[ORG] Я, как клиент, хочу переформить юрлица номер юр.лица на себя</v>
+      </c>
+      <c r="D60" t="str">
+        <v/>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>[SUPPORT] Обслуживание</v>
+      </c>
+      <c r="B61" t="str">
+        <v>[LOCK] Добровольная блокировка разблокировка</v>
+      </c>
+      <c r="C61" t="str">
+        <v>[ADD] Я, как клиент, хочу добровольно заблокировать свой  мобильный номер телефона</v>
+      </c>
+      <c r="D61" t="str">
+        <v/>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+      <c r="H61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>[SUPPORT] Обслуживание</v>
+      </c>
+      <c r="B62" t="str">
+        <v>[LOCK] Добровольная блокировка разблокировка</v>
+      </c>
+      <c r="C62" t="str">
+        <v>[REMOVE] Я, как клиент, хочу разблокировать свой мобильный номер телефона</v>
+      </c>
+      <c r="D62" t="str">
+        <v/>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+      <c r="H62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>[SUPPORT] Обслуживание</v>
+      </c>
+      <c r="B63" t="str">
+        <v>[LOCK] Добровольная блокировка разблокировка</v>
+      </c>
+      <c r="C63" t="str">
+        <v>[ADDFIX] Я, как клиент, хочу добровольно заблокировать домашиний интернет</v>
+      </c>
+      <c r="D63" t="str">
+        <v/>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+      <c r="H63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>[SUPPORT] Обслуживание</v>
+      </c>
+      <c r="B64" t="str">
+        <v>[LOCK] Добровольная блокировка разблокировка</v>
+      </c>
+      <c r="C64" t="str">
+        <v>[REMOVEFIX] Я, как клиент, хочу разблокировать домашний интернет</v>
+      </c>
+      <c r="D64" t="str">
+        <v/>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+      <c r="H64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>[SUPPORT] Обслуживание</v>
+      </c>
+      <c r="B65" t="str">
+        <v>[PIN] Восстановление PIN\PUK</v>
+      </c>
+      <c r="C65" t="str">
+        <v>[PUK] Я, как клиент, хочу разблокировать SIM и восстановить PIN с использованием PUK кода</v>
+      </c>
+      <c r="D65" t="str">
+        <v/>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+      <c r="H65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>[SUPPORT] Обслуживание</v>
+      </c>
+      <c r="B66" t="str">
+        <v>[PIN] Восстановление PIN\PUK</v>
+      </c>
+      <c r="C66" t="str">
+        <v>[CALL] Я, как клиент, хочу разбокировать SIM и восстановить PIN звонком по телефону</v>
+      </c>
+      <c r="D66" t="str">
+        <v/>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+      <c r="H66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>[SUPPORT] Обслуживание</v>
+      </c>
+      <c r="B67" t="str">
+        <v>[PIN] Восстановление PIN\PUK</v>
+      </c>
+      <c r="C67" t="str">
+        <v>[OFFICE] Я, как клиент, хочу разблокировать SIM и восстановить PIN в офисе билайн</v>
+      </c>
+      <c r="D67" t="str">
+        <v/>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v/>
+      </c>
+      <c r="G67" t="str">
+        <v/>
+      </c>
+      <c r="H67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>[SUPPORT] Обслуживание</v>
+      </c>
+      <c r="B68" t="str">
+        <v>[CTE] Сервисное обслуживание АБО (работа с возвратами, браком, ТВП, расхождениями и прочее)</v>
+      </c>
+      <c r="C68" t="str">
+        <v>ТБД</v>
+      </c>
+      <c r="D68" t="str">
+        <v/>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v/>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+      <c r="H68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>[SUPPORT] Обслуживание</v>
+      </c>
+      <c r="B69" t="str">
+        <v>[IMPROVE-MOBILE] Регламент "Улучшение покрытия мобильной сети для абонентов В2В"</v>
+      </c>
+      <c r="C69" t="str">
+        <v>ТБД</v>
+      </c>
+      <c r="D69" t="str">
+        <v/>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v/>
+      </c>
+      <c r="G69" t="str">
+        <v/>
+      </c>
+      <c r="H69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>[SUPPORT] Обслуживание</v>
+      </c>
+      <c r="B70" t="str">
+        <v>[TRANSFER] Переезд</v>
+      </c>
+      <c r="C70" t="str">
+        <v>[FIX] Я, как клиент, хочу перенести домашний интернет на новую квартиру</v>
+      </c>
+      <c r="D70" t="str">
+        <v/>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+      <c r="H70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>[FINANCE] Оплата и финансы</v>
+      </c>
+      <c r="B71" t="str">
+        <v>[PAY] Оплата с ЛС</v>
+      </c>
+      <c r="C71" t="str">
+        <v>[FEE] Я, как клиент, хочу оплатить абоненскую плату с баланса ЛС</v>
+      </c>
+      <c r="D71" t="str">
+        <v/>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71" t="str">
+        <v/>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
+      <c r="H71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>[FINANCE] Оплата и финансы</v>
+      </c>
+      <c r="B72" t="str">
+        <v>[PAY] Оплата с ЛС</v>
+      </c>
+      <c r="C72" t="str">
+        <v>[MOBILE] Я, как клиент, хочу провести оплату через мобильный платеж</v>
+      </c>
+      <c r="D72" t="str">
+        <v/>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+      <c r="F72" t="str">
+        <v/>
+      </c>
+      <c r="G72" t="str">
+        <v/>
+      </c>
+      <c r="H72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>[FINANCE] Оплата и финансы</v>
+      </c>
+      <c r="B73" t="str">
+        <v>[PAY] Оплата с ЛС</v>
+      </c>
+      <c r="C73" t="str">
+        <v>[ISHOP] Я, как клиент, хочу провести оплату в интеренете через мобильный платеж</v>
+      </c>
+      <c r="D73" t="str">
+        <v/>
+      </c>
+      <c r="E73" t="str">
+        <v/>
+      </c>
+      <c r="F73" t="str">
+        <v/>
+      </c>
+      <c r="G73" t="str">
+        <v/>
+      </c>
+      <c r="H73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>[FINANCE] Оплата и финансы</v>
+      </c>
+      <c r="B74" t="str">
+        <v>[PAY] Оплата с ЛС</v>
+      </c>
+      <c r="C74" t="str">
+        <v>[APPSTORE] Я, как клиент, хочу провести оплату в app story/google play через мобильный платеж</v>
+      </c>
+      <c r="D74" t="str">
+        <v/>
+      </c>
+      <c r="E74" t="str">
+        <v/>
+      </c>
+      <c r="F74" t="str">
+        <v/>
+      </c>
+      <c r="G74" t="str">
+        <v/>
+      </c>
+      <c r="H74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>[FINANCE] Оплата и финансы</v>
+      </c>
+      <c r="B75" t="str">
+        <v>[PAY] Оплата с ЛС</v>
+      </c>
+      <c r="C75" t="str">
+        <v>[TRANSFER] Я, как клиент, хочу сделать перевод с мобильного ЛС</v>
+      </c>
+      <c r="D75" t="str">
+        <v/>
+      </c>
+      <c r="E75" t="str">
+        <v/>
+      </c>
+      <c r="F75" t="str">
+        <v/>
+      </c>
+      <c r="G75" t="str">
+        <v/>
+      </c>
+      <c r="H75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>[FINANCE] Оплата и финансы</v>
+      </c>
+      <c r="B76" t="str">
+        <v>[PAY] Оплата с ЛС</v>
+      </c>
+      <c r="C76" t="str">
+        <v>[SMS] Я, как клиент, хочу оплатить по SMS с мобильного ЛС</v>
+      </c>
+      <c r="D76" t="str">
+        <v/>
+      </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+      <c r="F76" t="str">
+        <v/>
+      </c>
+      <c r="G76" t="str">
+        <v/>
+      </c>
+      <c r="H76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>[FINANCE] Оплата и финансы</v>
+      </c>
+      <c r="B77" t="str">
+        <v>[PAY] Оплата с ЛС</v>
+      </c>
+      <c r="C77" t="str">
+        <v>[SOCIAL] Я, как клиент, хочу сделать платеж в соц.сетях с мобильного ЛС</v>
+      </c>
+      <c r="D77" t="str">
+        <v/>
+      </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
+      <c r="F77" t="str">
+        <v/>
+      </c>
+      <c r="G77" t="str">
+        <v/>
+      </c>
+      <c r="H77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>[FINANCE] Оплата и финансы</v>
+      </c>
+      <c r="B78" t="str">
+        <v>[PAY] Оплата с ЛС</v>
+      </c>
+      <c r="C78" t="str">
+        <v>[CREDIT] Я, как клиент, хочу погасить кредит с мобильного ЛС</v>
+      </c>
+      <c r="D78" t="str">
+        <v/>
+      </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+      <c r="F78" t="str">
+        <v/>
+      </c>
+      <c r="G78" t="str">
+        <v/>
+      </c>
+      <c r="H78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>[FINANCE] Оплата и финансы</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Доверительный платеж</v>
+      </c>
+      <c r="C79" t="str">
+        <v>[TRUST] Я, как клиент, хочу подключить доверительный платеж</v>
+      </c>
+      <c r="D79" t="str">
+        <v/>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79" t="str">
+        <v/>
+      </c>
+      <c r="G79" t="str">
+        <v/>
+      </c>
+      <c r="H79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>[FINANCE] Оплата и финансы</v>
+      </c>
+      <c r="B80" t="str">
+        <v>[BALANCE] Управление балансами ЛС</v>
+      </c>
+      <c r="C80" t="str">
+        <v>[BEELINE.RU] Я, как клиент, хочу пополнить баланс с сайта beeline.ru</v>
+      </c>
+      <c r="D80" t="str">
+        <v/>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+      <c r="F80" t="str">
+        <v/>
+      </c>
+      <c r="G80" t="str">
+        <v/>
+      </c>
+      <c r="H80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>[FINANCE] Оплата и финансы</v>
+      </c>
+      <c r="B81" t="str">
+        <v>[BALANCE] Управление балансами ЛС</v>
+      </c>
+      <c r="C81" t="str">
+        <v>[APP] Я, как клиент, хочу пополнить баланс из мобильного приложения</v>
+      </c>
+      <c r="D81" t="str">
+        <v/>
+      </c>
+      <c r="E81" t="str">
+        <v/>
+      </c>
+      <c r="F81" t="str">
+        <v/>
+      </c>
+      <c r="G81" t="str">
+        <v/>
+      </c>
+      <c r="H81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>[FINANCE] Оплата и финансы</v>
+      </c>
+      <c r="B82" t="str">
+        <v>[BALANCE] Управление балансами ЛС</v>
+      </c>
+      <c r="C82" t="str">
+        <v>[BANKAPP] Я, как клиент, хочу попонить баланс из банковского приложения</v>
+      </c>
+      <c r="D82" t="str">
+        <v/>
+      </c>
+      <c r="E82" t="str">
+        <v/>
+      </c>
+      <c r="F82" t="str">
+        <v/>
+      </c>
+      <c r="G82" t="str">
+        <v/>
+      </c>
+      <c r="H82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>[FINANCE] Оплата и финансы</v>
+      </c>
+      <c r="B83" t="str">
+        <v>[BALANCE] Управление балансами ЛС</v>
+      </c>
+      <c r="C83" t="str">
+        <v>[ATM] Я, как клиент, хочу пополнить баланс через банкомат</v>
+      </c>
+      <c r="D83" t="str">
+        <v/>
+      </c>
+      <c r="E83" t="str">
+        <v/>
+      </c>
+      <c r="F83" t="str">
+        <v/>
+      </c>
+      <c r="G83" t="str">
+        <v/>
+      </c>
+      <c r="H83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>[FINANCE] Оплата и финансы</v>
+      </c>
+      <c r="B84" t="str">
+        <v>[BALANCE] Управление балансами ЛС</v>
+      </c>
+      <c r="C84" t="str">
+        <v>[TERMINAL] Я, как клиент, хочу пополнить баланс через терминал оплаты</v>
+      </c>
+      <c r="D84" t="str">
+        <v/>
+      </c>
+      <c r="E84" t="str">
+        <v/>
+      </c>
+      <c r="F84" t="str">
+        <v/>
+      </c>
+      <c r="G84" t="str">
+        <v/>
+      </c>
+      <c r="H84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>[FINANCE] Оплата и финансы</v>
+      </c>
+      <c r="B85" t="str">
+        <v>[BALANCE] Управление балансами ЛС</v>
+      </c>
+      <c r="C85" t="str">
+        <v>[CASH] Я, как клиент, хочу поплнить баланс наличными в офисе билайн</v>
+      </c>
+      <c r="D85" t="str">
+        <v/>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85" t="str">
+        <v/>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+      <c r="H85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>[FINANCE] Оплата и финансы</v>
+      </c>
+      <c r="B86" t="str">
+        <v>[BALANCE] Управление балансами ЛС</v>
+      </c>
+      <c r="C86" t="str">
+        <v>[EVALLET] Я, как клиент, хочу пополнить баланс с электронного кошелька</v>
+      </c>
+      <c r="D86" t="str">
+        <v/>
+      </c>
+      <c r="E86" t="str">
+        <v/>
+      </c>
+      <c r="F86" t="str">
+        <v/>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
+      <c r="H86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>[FINANCE] Оплата и финансы</v>
+      </c>
+      <c r="B87" t="str">
+        <v>[BALANCE] Управление балансами ЛС</v>
+      </c>
+      <c r="C87" t="str">
+        <v>[PHONE] Я, как клиент, хочу пополнить баланс с другого мобильного ЛС на сайте</v>
+      </c>
+      <c r="D87" t="str">
+        <v/>
+      </c>
+      <c r="E87" t="str">
+        <v/>
+      </c>
+      <c r="F87" t="str">
+        <v/>
+      </c>
+      <c r="G87" t="str">
+        <v/>
+      </c>
+      <c r="H87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>[FINANCE] Оплата и финансы</v>
+      </c>
+      <c r="B88" t="str">
+        <v>[BALANCE] Управление балансами ЛС</v>
+      </c>
+      <c r="C88" t="str">
+        <v>[SMS] Я, как клиент, хочу пополнить баланс с другого мобильного ЛС через СМС</v>
+      </c>
+      <c r="D88" t="str">
+        <v/>
+      </c>
+      <c r="E88" t="str">
+        <v/>
+      </c>
+      <c r="F88" t="str">
+        <v/>
+      </c>
+      <c r="G88" t="str">
+        <v/>
+      </c>
+      <c r="H88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>[FINANCE] Оплата и финансы</v>
+      </c>
+      <c r="B89" t="str">
+        <v>[BALANCE] Управление балансами ЛС</v>
+      </c>
+      <c r="C89" t="str">
+        <v>[AUTO] Я, как клиент, хочу настроить автоплатеж</v>
+      </c>
+      <c r="D89" t="str">
+        <v/>
+      </c>
+      <c r="E89" t="str">
+        <v/>
+      </c>
+      <c r="F89" t="str">
+        <v/>
+      </c>
+      <c r="G89" t="str">
+        <v/>
+      </c>
+      <c r="H89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>[FINANCE] Оплата и финансы</v>
+      </c>
+      <c r="B90" t="str">
+        <v>[BALANCE] Управление балансами ЛС</v>
+      </c>
+      <c r="C90" t="str">
+        <v>[EXTRA] Я, как клиент, хочу пополнить дополнительный баланс для мобильной оплаты</v>
+      </c>
+      <c r="D90" t="str">
+        <v/>
+      </c>
+      <c r="E90" t="str">
+        <v/>
+      </c>
+      <c r="F90" t="str">
+        <v/>
+      </c>
+      <c r="G90" t="str">
+        <v/>
+      </c>
+      <c r="H90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>[FINANCE] Оплата и финансы</v>
+      </c>
+      <c r="B91" t="str">
+        <v>[BALANCE] Управление балансами ЛС</v>
+      </c>
+      <c r="C91" t="str">
+        <v>[LK-INFO] Я, как клиент, хочу посмотреть баланс в ЕЛК</v>
+      </c>
+      <c r="D91" t="str">
+        <v/>
+      </c>
+      <c r="E91" t="str">
+        <v/>
+      </c>
+      <c r="F91" t="str">
+        <v/>
+      </c>
+      <c r="G91" t="str">
+        <v/>
+      </c>
+      <c r="H91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>[FINANCE] Оплата и финансы</v>
+      </c>
+      <c r="B92" t="str">
+        <v>[BALANCE] Управление балансами ЛС</v>
+      </c>
+      <c r="C92" t="str">
+        <v>[APP-INFO] Я, как клиент, хочу посмотреть баланс в мобильном приложении</v>
+      </c>
+      <c r="D92" t="str">
+        <v/>
+      </c>
+      <c r="E92" t="str">
+        <v/>
+      </c>
+      <c r="F92" t="str">
+        <v/>
+      </c>
+      <c r="G92" t="str">
+        <v/>
+      </c>
+      <c r="H92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>[FINANCE] Оплата и финансы</v>
+      </c>
+      <c r="B93" t="str">
+        <v>[BALANCE] Управление балансами ЛС</v>
+      </c>
+      <c r="C93" t="str">
+        <v>[SMS-INFO] Я, как клиент, хочу получить информацию о балансе через СМС</v>
+      </c>
+      <c r="D93" t="str">
+        <v/>
+      </c>
+      <c r="E93" t="str">
+        <v/>
+      </c>
+      <c r="F93" t="str">
+        <v/>
+      </c>
+      <c r="G93" t="str">
+        <v/>
+      </c>
+      <c r="H93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>[FINANCE] Оплата и финансы</v>
+      </c>
+      <c r="B94" t="str">
+        <v>[ERR] Ошибочный платеж</v>
+      </c>
+      <c r="C94" t="str">
+        <v>[RETURN] Я, как клиент, хочу вернуть ошибочный платеж</v>
+      </c>
+      <c r="D94" t="str">
+        <v/>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
+        <v/>
+      </c>
+      <c r="G94" t="str">
+        <v/>
+      </c>
+      <c r="H94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>[FINANCE] Оплата и финансы</v>
+      </c>
+      <c r="B95" t="str">
+        <v>[DETAILS] Просмотр детализации и истории платежей</v>
+      </c>
+      <c r="C95" t="str">
+        <v>[ELK] Я, как клиент, хочу получить детализацию начислений через ЕЛК</v>
+      </c>
+      <c r="D95" t="str">
+        <v/>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
+        <v/>
+      </c>
+      <c r="G95" t="str">
+        <v/>
+      </c>
+      <c r="H95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>[FINANCE] Оплата и финансы</v>
+      </c>
+      <c r="B96" t="str">
+        <v>[DETAILS] Просмотр детализации и истории платежей</v>
+      </c>
+      <c r="C96" t="str">
+        <v>[APP] Я, как клиент, хочу получить детализацию через мобильное приложение</v>
+      </c>
+      <c r="D96" t="str">
+        <v/>
+      </c>
+      <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
+        <v/>
+      </c>
+      <c r="G96" t="str">
+        <v/>
+      </c>
+      <c r="H96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>[FINANCE] Оплата и финансы</v>
+      </c>
+      <c r="B97" t="str">
+        <v>[DETAILS] Просмотр детализации и истории платежей</v>
+      </c>
+      <c r="C97" t="str">
+        <v>[PAY-ELK] Я, как клиент, хочу получить историю пополнений через ЕЛК</v>
+      </c>
+      <c r="D97" t="str">
+        <v/>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
+        <v/>
+      </c>
+      <c r="G97" t="str">
+        <v/>
+      </c>
+      <c r="H97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>[FINANCE] Оплата и финансы</v>
+      </c>
+      <c r="B98" t="str">
+        <v>[DETAILS] Просмотр детализации и истории платежей</v>
+      </c>
+      <c r="C98" t="str">
+        <v>[PAY-APP] Я, как клиент, хочу получить историю поплнений через мобильное приложение</v>
+      </c>
+      <c r="D98" t="str">
+        <v/>
+      </c>
+      <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
+        <v/>
+      </c>
+      <c r="G98" t="str">
+        <v/>
+      </c>
+      <c r="H98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>[FINANCE] Оплата и финансы</v>
+      </c>
+      <c r="B99" t="str">
+        <v>[PAYMETHOD] Управление методами оплаты</v>
+      </c>
+      <c r="C99" t="str">
+        <v>[CHANGE] Я, как клиент, хочу сменить метод оплаты</v>
+      </c>
+      <c r="D99" t="str">
+        <v/>
+      </c>
+      <c r="E99" t="str">
+        <v/>
+      </c>
+      <c r="F99" t="str">
+        <v/>
+      </c>
+      <c r="G99" t="str">
+        <v/>
+      </c>
+      <c r="H99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>[FINANCE] Оплата и финансы</v>
+      </c>
+      <c r="B100" t="str">
+        <v>[BILLING] Формирование счета</v>
+      </c>
+      <c r="C100" t="str">
+        <v>ТБД</v>
+      </c>
+      <c r="D100" t="str">
+        <v/>
+      </c>
+      <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
+        <v/>
+      </c>
+      <c r="G100" t="str">
+        <v/>
+      </c>
+      <c r="H100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>[FINANCE] Оплата и финансы</v>
+      </c>
+      <c r="B101" t="str">
+        <v>[CORRECTION]</v>
+      </c>
+      <c r="C101" t="str">
+        <v>Предоставление разовых корректировок</v>
+      </c>
+      <c r="D101" t="str">
+        <v/>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
+        <v/>
+      </c>
+      <c r="G101" t="str">
+        <v/>
+      </c>
+      <c r="H101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>[FINANCE] Оплата и финансы</v>
+      </c>
+      <c r="B102" t="str">
+        <v>[DELIVERY] Печать и доставка счета</v>
+      </c>
+      <c r="C102" t="str">
+        <v>ТБД</v>
+      </c>
+      <c r="D102" t="str">
+        <v/>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
+        <v/>
+      </c>
+      <c r="G102" t="str">
+        <v/>
+      </c>
+      <c r="H102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>[REQUEST] Обращения</v>
+      </c>
+      <c r="B103" t="str">
+        <v>[INFO] Консультации</v>
+      </c>
+      <c r="C103" t="str">
+        <v>ТБД</v>
+      </c>
+      <c r="D103" t="str">
+        <v/>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
+        <v/>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+      <c r="H103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>[REQUEST] Обращения</v>
+      </c>
+      <c r="B104" t="str">
+        <v>[CLAIMS] Претензии</v>
+      </c>
+      <c r="C104" t="str">
+        <v>ТБД</v>
+      </c>
+      <c r="D104" t="str">
+        <v/>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
+        <v/>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+      <c r="H104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>[LOYALTY] Управление лояльностью</v>
+      </c>
+      <c r="B105" t="str">
+        <v>ТБД</v>
+      </c>
+      <c r="C105" t="str">
+        <v/>
+      </c>
+      <c r="D105" t="str">
+        <v/>
+      </c>
+      <c r="E105" t="str">
+        <v/>
+      </c>
+      <c r="F105" t="str">
+        <v/>
+      </c>
+      <c r="G105" t="str">
+        <v/>
+      </c>
+      <c r="H105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>[PRODUCT] Управление продуктовыми каталогом</v>
+      </c>
+      <c r="B106" t="str">
+        <v>ТБД</v>
+      </c>
+      <c r="C106" t="str">
+        <v/>
+      </c>
+      <c r="D106" t="str">
+        <v/>
+      </c>
+      <c r="E106" t="str">
+        <v/>
+      </c>
+      <c r="F106" t="str">
+        <v/>
+      </c>
+      <c r="G106" t="str">
+        <v/>
+      </c>
+      <c r="H106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>[PARTNER] Управление партнерами</v>
+      </c>
+      <c r="B107" t="str">
+        <v>[AGENT] Процедура по работе с Агентами</v>
+      </c>
+      <c r="C107" t="str">
+        <v/>
+      </c>
+      <c r="D107" t="str">
+        <v/>
+      </c>
+      <c r="E107" t="str">
+        <v/>
+      </c>
+      <c r="F107" t="str">
+        <v/>
+      </c>
+      <c r="G107" t="str">
+        <v/>
+      </c>
+      <c r="H107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>[PARTNER] Управление партнерами</v>
+      </c>
+      <c r="B108" t="str">
+        <v>[TENDER] Процедура по работе с тендерами</v>
+      </c>
+      <c r="C108" t="str">
+        <v/>
+      </c>
+      <c r="D108" t="str">
+        <v/>
+      </c>
+      <c r="E108" t="str">
+        <v/>
+      </c>
+      <c r="F108" t="str">
+        <v/>
+      </c>
+      <c r="G108" t="str">
+        <v/>
+      </c>
+      <c r="H108" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A2:A3"/>
+  <mergeCells count="28">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B5:B11"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="B19:B24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="A5:A26"/>
+    <mergeCell ref="A27:A31"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="B36:B39"/>
+    <mergeCell ref="A32:A39"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="B40:B43"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="B47:B50"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B61:B64"/>
+    <mergeCell ref="B65:B67"/>
+    <mergeCell ref="A40:A70"/>
+    <mergeCell ref="B71:B78"/>
+    <mergeCell ref="B80:B93"/>
+    <mergeCell ref="B95:B98"/>
+    <mergeCell ref="A71:A102"/>
+    <mergeCell ref="A103:A104"/>
+    <mergeCell ref="A107:A108"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H108"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/dashboard-new.xlsx
+++ b/data/dashboard-new.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H108"/>
+  <dimension ref="A1:H125"/>
   <cols>
     <col min="1" max="1" width="25.83203125" customWidth="1"/>
     <col min="2" max="2" width="35.83203125" customWidth="1"/>
@@ -437,13 +437,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>[CUST] Управление клиентами</v>
+        <v>[PRODUCT] Управление продуктовыми каталогом</v>
       </c>
       <c r="B2" t="str">
-        <v>Персональные менеджеры</v>
+        <v>ТБД</v>
       </c>
       <c r="C2" t="str">
-        <v>Закрепление/открепление/изменение Личного Оператора</v>
+        <v/>
       </c>
       <c r="D2" t="str">
         <v/>
@@ -463,91 +463,91 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>[CUST] Управление клиентами</v>
+        <v>[PRODUCT] Управление продуктовыми каталогом</v>
       </c>
       <c r="B3" t="str">
-        <v>Создание(изменение) Группы Компании/Добавление Компании в ГК</v>
+        <v>[RETAIL] Управление розничными продуктами</v>
       </c>
       <c r="C3" t="str">
-        <v/>
+        <v>[GOODS] Я, как сотрудник компании, управляю розничными товарами</v>
       </c>
       <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
+        <v>4.1 Заведение номенклатуры товаров B2C в ИТ-системы компании</v>
+      </c>
+      <c r="E3">
+        <v>42</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>11</v>
+      </c>
+      <c r="H3">
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>[CUST] Управление клиентами</v>
+        <v>[PRODUCT] Управление продуктовыми каталогом</v>
       </c>
       <c r="B4" t="str">
-        <v>[GOVERNANCE] Работа с государственными клиентами</v>
+        <v>[CONNECT_B2B] Управление предложением услуг связи B2B</v>
       </c>
       <c r="C4" t="str">
-        <v/>
+        <v>[MOBILE] Я, как сотрудник компании, создаю новый тарифный план B2B</v>
       </c>
       <c r="D4" t="str">
-        <v/>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
+        <v>4.2 Я как маркетолог создаю новый postpaid ТП мобильной связи B2B</v>
+      </c>
+      <c r="E4">
+        <v>74</v>
+      </c>
+      <c r="F4">
+        <v>5</v>
+      </c>
+      <c r="G4">
+        <v>6</v>
+      </c>
+      <c r="H4">
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>[SALE] Продажи</v>
+        <v>[PRODUCT] Управление продуктовыми каталогом</v>
       </c>
       <c r="B5" t="str">
-        <v>[CONNECT] Продажа услуг связи</v>
+        <v>[CONNECT_B2B] Управление предложением услуг связи B2B</v>
       </c>
       <c r="C5" t="str">
-        <v>[SIM] Я, как клиент, покупаю SIM новую карту</v>
+        <v>[MOBILE] Я, как сотрудник компании, создаю новый тарифный план B2B</v>
       </c>
       <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
+        <v xml:space="preserve">01 Синхронизация элементов разнесения выручки из Арены в BIIS </v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>[SALE] Продажи</v>
+        <v>[REQUEST] Обращения</v>
       </c>
       <c r="B6" t="str">
-        <v>[CONNECT] Продажа услуг связи</v>
+        <v>[CLAIMS] Претензии</v>
       </c>
       <c r="C6" t="str">
-        <v>Я, как клиент покупаю новую сим-карту с красивым номером</v>
+        <v>ТБД</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -567,13 +567,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>[SALE] Продажи</v>
+        <v>[REQUEST] Обращения</v>
       </c>
       <c r="B7" t="str">
-        <v>[CONNECT] Продажа услуг связи</v>
+        <v>[INFO] Консультации</v>
       </c>
       <c r="C7" t="str">
-        <v>[NUMBER] Я, как клиент, хочу купить красивый номер на существующую СИМ карту</v>
+        <v>ТБД</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -593,13 +593,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>[SALE] Продажи</v>
+        <v>[SUPPORT] Обслуживание</v>
       </c>
       <c r="B8" t="str">
-        <v>[CONNECT] Продажа услуг связи</v>
+        <v>[TRANSFER] Переезд</v>
       </c>
       <c r="C8" t="str">
-        <v>[ESIM] Я, как клиент, хочу купить eSIM</v>
+        <v>[FIX] Я, как клиент, хочу перенести домашний интернет на новую квартиру</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -619,13 +619,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>[SALE] Продажи</v>
+        <v>[SUPPORT] Обслуживание</v>
       </c>
       <c r="B9" t="str">
-        <v>[CONNECT] Продажа услуг связи</v>
+        <v>[IMPROVE-MOBILE] Регламент "Улучшение покрытия мобильной сети для абонентов В2В"</v>
       </c>
       <c r="C9" t="str">
-        <v>[MNP] Я, как клиент, хочу перейти в билайн с сохранением номера</v>
+        <v>ТБД</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -645,13 +645,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>[SALE] Продажи</v>
+        <v>[SUPPORT] Обслуживание</v>
       </c>
       <c r="B10" t="str">
-        <v>[CONNECT] Продажа услуг связи</v>
+        <v>[CTE] Сервисное обслуживание АБО (работа с возвратами, браком, ТВП, расхождениями и прочее)</v>
       </c>
       <c r="C10" t="str">
-        <v>[FIX] Я, как клиент, хочу купить домашний интернет и ТВ</v>
+        <v>ТБД</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -671,13 +671,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>[SALE] Продажи</v>
+        <v>[SUPPORT] Обслуживание</v>
       </c>
       <c r="B11" t="str">
-        <v>[CONNECT] Продажа услуг связи</v>
+        <v>[PIN] Восстановление PIN\PUK</v>
       </c>
       <c r="C11" t="str">
-        <v>[RESTORE] Я, как клиент, хочу восстановить свой номер телефона и купить мобильную связь билайн</v>
+        <v>[OFFICE] Я, как клиент, хочу разблокировать SIM и восстановить PIN в офисе билайн</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -697,13 +697,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>[SALE] Продажи</v>
+        <v>[SUPPORT] Обслуживание</v>
       </c>
       <c r="B12" t="str">
-        <v>[CONVERGENT] Продажа конвергентных продуктов</v>
+        <v>[PIN] Восстановление PIN\PUK</v>
       </c>
       <c r="C12" t="str">
-        <v>[NEWSIM] Я, как клиент, хочу подключить домашний интернет, ТВ билайн и купить новую SIM</v>
+        <v>[CALL] Я, как клиент, хочу разбокировать SIM и восстановить PIN звонком по телефону</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -723,13 +723,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>[SALE] Продажи</v>
+        <v>[SUPPORT] Обслуживание</v>
       </c>
       <c r="B13" t="str">
-        <v>[CONVERGENT] Продажа конвергентных продуктов</v>
+        <v>[PIN] Восстановление PIN\PUK</v>
       </c>
       <c r="C13" t="str">
-        <v>[PACKAGE] Я, как клиент, хочу подключить домашний интернет, ТВ билайн и сменить тариф на существующем номере</v>
+        <v>[PUK] Я, как клиент, хочу разблокировать SIM и восстановить PIN с использованием PUK кода</v>
       </c>
       <c r="D13" t="str">
         <v/>
@@ -749,13 +749,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>[SALE] Продажи</v>
+        <v>[SUPPORT] Обслуживание</v>
       </c>
       <c r="B14" t="str">
-        <v>[CONVERGENT] Продажа конвергентных продуктов</v>
+        <v>[LOCK] Добровольная блокировка разблокировка</v>
       </c>
       <c r="C14" t="str">
-        <v>[NEWESIM] Я, как клиент, хочу подключить домашний интернет, ТВ билайн и и купить eSIM</v>
+        <v>[REMOVEFIX] Я, как клиент, хочу разблокировать домашний интернет</v>
       </c>
       <c r="D14" t="str">
         <v/>
@@ -775,13 +775,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>[SALE] Продажи</v>
+        <v>[SUPPORT] Обслуживание</v>
       </c>
       <c r="B15" t="str">
-        <v>[CONVERGENT] Продажа конвергентных продуктов</v>
+        <v>[LOCK] Добровольная блокировка разблокировка</v>
       </c>
       <c r="C15" t="str">
-        <v>[MNP] Я, как клиент, хочу подключить домашний интернет, ТВ билайн и перейти по MNP с сохранением своего номера</v>
+        <v>[ADDFIX] Я, как клиент, хочу добровольно заблокировать домашиний интернет</v>
       </c>
       <c r="D15" t="str">
         <v/>
@@ -801,13 +801,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>[SALE] Продажи</v>
+        <v>[SUPPORT] Обслуживание</v>
       </c>
       <c r="B16" t="str">
-        <v>[CTE] Продажа и аренда фикс.оборудования</v>
+        <v>[LOCK] Добровольная блокировка разблокировка</v>
       </c>
       <c r="C16" t="str">
-        <v>[SALE] Я, как клиент, хочу купить обрудования для домашнего интернета и ТВ</v>
+        <v>[REMOVE] Я, как клиент, хочу разблокировать свой мобильный номер телефона</v>
       </c>
       <c r="D16" t="str">
         <v/>
@@ -827,13 +827,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>[SALE] Продажи</v>
+        <v>[SUPPORT] Обслуживание</v>
       </c>
       <c r="B17" t="str">
-        <v>[CTE] Продажа и аренда фикс.оборудования</v>
+        <v>[LOCK] Добровольная блокировка разблокировка</v>
       </c>
       <c r="C17" t="str">
-        <v>[RENT] Я, как клиент, хочу взять в аренту оборудование для домашнего интернета и ТВ</v>
+        <v>[ADD] Я, как клиент, хочу добровольно заблокировать свой  мобильный номер телефона</v>
       </c>
       <c r="D17" t="str">
         <v/>
@@ -853,13 +853,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>[SALE] Продажи</v>
+        <v>[SUPPORT] Обслуживание</v>
       </c>
       <c r="B18" t="str">
-        <v>[CTE] Продажа и аренда фикс.оборудования</v>
+        <v>[OWNER] Смена владельца номера</v>
       </c>
       <c r="C18" t="str">
-        <v>[RETURNS] Я, как клиент, врзвращаю оборудование</v>
+        <v>[ORG] Я, как клиент, хочу переформить юрлица номер юр.лица на себя</v>
       </c>
       <c r="D18" t="str">
         <v/>
@@ -879,13 +879,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>[SALE] Продажи</v>
+        <v>[SUPPORT] Обслуживание</v>
       </c>
       <c r="B19" t="str">
-        <v>[RETAIL] Розничные продажи</v>
+        <v>[OWNER] Смена владельца номера</v>
       </c>
       <c r="C19" t="str">
-        <v>[GOODS] Я, как клиент, хочу купить товар</v>
+        <v>[IDENTIFY] Я, как клиент, хочу переформить мобильный номер на себя с альтернативной идентификацией</v>
       </c>
       <c r="D19" t="str">
         <v/>
@@ -905,13 +905,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>[SALE] Продажи</v>
+        <v>[SUPPORT] Обслуживание</v>
       </c>
       <c r="B20" t="str">
-        <v>[RETAIL] Розничные продажи</v>
+        <v>[OWNER] Смена владельца номера</v>
       </c>
       <c r="C20" t="str">
-        <v>[TRADEIN] Я, как клиент, хочу купить товар в trade-in</v>
+        <v>[INDIVIDUAL] Я, как клиент, хочу переормить мобильный номер другого человека на себя</v>
       </c>
       <c r="D20" t="str">
         <v/>
@@ -931,13 +931,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>[SALE] Продажи</v>
+        <v>[SUPPORT] Обслуживание</v>
       </c>
       <c r="B21" t="str">
-        <v>[RETAIL] Розничные продажи</v>
+        <v>[INFO] Изменение/подтверждение персональных данных</v>
       </c>
       <c r="C21" t="str">
-        <v>Я, как клиент, хочу купить товар в интернет-магазине</v>
+        <v>[CONTRACT] я, как клиент изменяю данные по договору/клиенту (изменение ИНН, наименования, КПП, адреса, контактного лица и прочее)</v>
       </c>
       <c r="D21" t="str">
         <v/>
@@ -957,13 +957,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>[SALE] Продажи</v>
+        <v>[SUPPORT] Обслуживание</v>
       </c>
       <c r="B22" t="str">
-        <v>[RETAIL] Розничные продажи</v>
+        <v>[INFO] Изменение/подтверждение персональных данных</v>
       </c>
       <c r="C22" t="str">
-        <v>[DIGITAL] Я, как клиент, хочу купить цифровой продукт</v>
+        <v>[OFFICE] Я, как клиент, хочу обновить персональные данные в офисе билайн</v>
       </c>
       <c r="D22" t="str">
         <v/>
@@ -983,13 +983,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>[SALE] Продажи</v>
+        <v>[SUPPORT] Обслуживание</v>
       </c>
       <c r="B23" t="str">
-        <v>[RETAIL] Розничные продажи</v>
+        <v>[INFO] Изменение/подтверждение персональных данных</v>
       </c>
       <c r="C23" t="str">
-        <v>[RETURNS] Я, как клиент, хочу сделать возврат товара</v>
+        <v>[ESIA] Я, как клиент, хочу обновить персональные данные через ГОСУСЛУГИ</v>
       </c>
       <c r="D23" t="str">
         <v/>
@@ -1009,13 +1009,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>[SALE] Продажи</v>
+        <v>[SUPPORT] Обслуживание</v>
       </c>
       <c r="B24" t="str">
-        <v>[RETAIL] Розничные продажи</v>
+        <v>[DEVICE] Замена SIM и номера</v>
       </c>
       <c r="C24" t="str">
-        <v>[CANCEL] Я, как клиент, отменяю заказ</v>
+        <v>[SIM] Я,  как  клиент, хочу поменять SIM карту</v>
       </c>
       <c r="D24" t="str">
         <v/>
@@ -1035,13 +1035,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>[SALE] Продажи</v>
+        <v>[SUPPORT] Обслуживание</v>
       </c>
       <c r="B25" t="str">
-        <v>[PLAY] Игры и развлечения</v>
+        <v>[DEVICE] Замена SIM и номера</v>
       </c>
       <c r="C25" t="str">
-        <v>[BOOKS] Я, как клиент, хочу купить подписку на билайн книги</v>
+        <v>[MSISDN] Я,  как клиент, хочу поменять номер телефона</v>
       </c>
       <c r="D25" t="str">
         <v/>
@@ -1061,13 +1061,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>[SALE] Продажи</v>
+        <v>[SUPPORT] Обслуживание</v>
       </c>
       <c r="B26" t="str">
-        <v>[PLAY] Игры и развлечения</v>
+        <v>[ACCOUNT] Управление аккаунтами</v>
       </c>
       <c r="C26" t="str">
-        <v>[CLOUD] Я, как клиент, хочу купить подписку на облако билайн</v>
+        <v>[APP] Я, как клиент, хчоу добавить аккаунт для управления в мобильном приложении</v>
       </c>
       <c r="D26" t="str">
         <v/>
@@ -1087,13 +1087,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>[AGREEMENT] Управление контрактами и условиями договоров</v>
+        <v>[SUPPORT] Обслуживание</v>
       </c>
       <c r="B27" t="str">
-        <v>[PRIVATE] Предоставление непубличных условий клиентам mob</v>
+        <v>[ACCOUNT] Управление аккаунтами</v>
       </c>
       <c r="C27" t="str">
-        <v>ТБД</v>
+        <v>[ELK] Я, как клиент, хочу добавить аккаунт для управления в ЕЛК</v>
       </c>
       <c r="D27" t="str">
         <v/>
@@ -1113,13 +1113,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>[AGREEMENT] Управление контрактами и условиями договоров</v>
+        <v>[SUPPORT] Обслуживание</v>
       </c>
       <c r="B28" t="str">
-        <v>ТБД Сохранение/расторжение Клиента</v>
+        <v>[FAMALY] Семья в билайн</v>
       </c>
       <c r="C28" t="str">
-        <v/>
+        <v>[INFO] Я, как клиент, хочу получить информацию о балансах близких</v>
       </c>
       <c r="D28" t="str">
         <v/>
@@ -1139,13 +1139,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>[AGREEMENT] Управление контрактами и условиями договоров</v>
+        <v>[SUPPORT] Обслуживание</v>
       </c>
       <c r="B29" t="str">
-        <v>[ARCHIVE] Архивация клиентской документации</v>
+        <v>[FAMALY] Семья в билайн</v>
       </c>
       <c r="C29" t="str">
-        <v/>
+        <v>[SHARE] Я, как клиент, хочу поделиться тарифом с близкими</v>
       </c>
       <c r="D29" t="str">
         <v/>
@@ -1165,13 +1165,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>[AGREEMENT] Управление контрактами и условиями договоров</v>
+        <v>[SUPPORT] Обслуживание</v>
       </c>
       <c r="B30" t="str">
-        <v>Работа с нерезидентами</v>
+        <v>[FAMALY] Семья в билайн</v>
       </c>
       <c r="C30" t="str">
-        <v/>
+        <v>[INCLUDE] Я, как клиент, хоче подключить близких в в Семью билайн</v>
       </c>
       <c r="D30" t="str">
         <v/>
@@ -1191,13 +1191,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>[AGREEMENT] Управление контрактами и условиями договоров</v>
+        <v>[SUPPORT] Обслуживание</v>
       </c>
       <c r="B31" t="str">
-        <v>[SLA] Предоставление уровня обслуживания (АТ,SM в том числе)</v>
+        <v>[FAMALY] Семья в билайн</v>
       </c>
       <c r="C31" t="str">
-        <v/>
+        <v>[SUBSCRIBE] Я, как клиент, хочу подключить подписку Все для семьи</v>
       </c>
       <c r="D31" t="str">
         <v/>
@@ -1217,13 +1217,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>[USE] Предоставление и тарификация услуг</v>
+        <v>[SUPPORT] Обслуживание</v>
       </c>
       <c r="B32" t="str">
-        <v>[CONNECT] Предоставление услуг связи</v>
+        <v>[SERVICE] Подключение/отключение услуг</v>
       </c>
       <c r="C32" t="str">
-        <v>[VOICE] Я, как клиент, хочу сделать голосовой звонок</v>
+        <v>[CONVERGENT] Я, как клиент, хочу поменять условия конвергентного тарифного плана</v>
       </c>
       <c r="D32" t="str">
         <v/>
@@ -1243,13 +1243,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>[USE] Предоставление и тарификация услуг</v>
+        <v>[SUPPORT] Обслуживание</v>
       </c>
       <c r="B33" t="str">
-        <v>[CONNECT] Предоставление услуг связи</v>
+        <v>[SERVICE] Подключение/отключение услуг</v>
       </c>
       <c r="C33" t="str">
-        <v>[SMS] Я, как клиент, хочу послать SMS</v>
+        <v>[FIX] Я, как клиент, хочу подключить или отключить услугу фиксированной связи</v>
       </c>
       <c r="D33" t="str">
         <v/>
@@ -1269,13 +1269,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>[USE] Предоставление и тарификация услуг</v>
+        <v>[SUPPORT] Обслуживание</v>
       </c>
       <c r="B34" t="str">
-        <v>[CONNECT] Предоставление услуг связи</v>
+        <v>[SERVICE] Подключение/отключение услуг</v>
       </c>
       <c r="C34" t="str">
-        <v>[INETMOBILE] Я, как клиент, хочу воспользоваться мобильным интернетом</v>
+        <v>[MOBILE] Я, как клиент, хочу подключить или отключить услугу на мобильном тарифном плане</v>
       </c>
       <c r="D34" t="str">
         <v/>
@@ -1295,13 +1295,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>[USE] Предоставление и тарификация услуг</v>
+        <v>[SUPPORT] Обслуживание</v>
       </c>
       <c r="B35" t="str">
-        <v>[CONNECT] Предоставление услуг связи</v>
+        <v>[TARIF] Смена тарифного плана</v>
       </c>
       <c r="C35" t="str">
-        <v>[INETFIX] Я, как клиент, хочу воспользоваться домашним интернетом</v>
+        <v>[CONVERGENT] Я, как клиент, хочу поменять условия конвергентного тарифного плана</v>
       </c>
       <c r="D35" t="str">
         <v/>
@@ -1321,13 +1321,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>[USE] Предоставление и тарификация услуг</v>
+        <v>[SUPPORT] Обслуживание</v>
       </c>
       <c r="B36" t="str">
-        <v>[VAS] Предоставление услуг VAS платформ</v>
+        <v>[TARIF] Смена тарифного плана</v>
       </c>
       <c r="C36" t="str">
-        <v>[TV] Я, как клиент, хочу посмотреть TV</v>
+        <v>[FIX] Я, как клиент, хочу сменить тарифный план на домашний интернет и ТВ</v>
       </c>
       <c r="D36" t="str">
         <v/>
@@ -1347,39 +1347,39 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>[USE] Предоставление и тарификация услуг</v>
+        <v>[SUPPORT] Обслуживание</v>
       </c>
       <c r="B37" t="str">
-        <v>[VAS] Предоставление услуг VAS платформ</v>
+        <v>[TARIF] Смена тарифного плана</v>
       </c>
       <c r="C37" t="str">
-        <v>[MOVIE] Я, как клиент, хочу посмотреть фильм на билайн ТВ</v>
+        <v>[MOBILE] Я, как клиент, хочу сменить мобильный тарифный план</v>
       </c>
       <c r="D37" t="str">
-        <v/>
-      </c>
-      <c r="E37" t="str">
-        <v/>
-      </c>
-      <c r="F37" t="str">
-        <v/>
-      </c>
-      <c r="G37" t="str">
-        <v/>
-      </c>
-      <c r="H37" t="str">
-        <v/>
+        <v>e2e Я, как клиент, перехожу на тарифный план UP в мобильном приложении</v>
+      </c>
+      <c r="E37">
+        <v>241</v>
+      </c>
+      <c r="F37">
+        <v>61</v>
+      </c>
+      <c r="G37">
+        <v>21</v>
+      </c>
+      <c r="H37">
+        <v>20</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>[USE] Предоставление и тарификация услуг</v>
+        <v>[FINANCE] Оплата и финансы</v>
       </c>
       <c r="B38" t="str">
-        <v>[VAS] Предоставление услуг VAS платформ</v>
+        <v>[DELIVERY] Печать и доставка счета</v>
       </c>
       <c r="C38" t="str">
-        <v>[BOOKS] Я, как клиент, хочу почитать книги билайн</v>
+        <v>ТБД</v>
       </c>
       <c r="D38" t="str">
         <v/>
@@ -1399,13 +1399,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>[USE] Предоставление и тарификация услуг</v>
+        <v>[FINANCE] Оплата и финансы</v>
       </c>
       <c r="B39" t="str">
-        <v>[VAS] Предоставление услуг VAS платформ</v>
+        <v>[CORRECTION]</v>
       </c>
       <c r="C39" t="str">
-        <v>[CLOUD] Я, как клиент, хоочу воспользоваться облаком билайн</v>
+        <v>Предоставление разовых корректировок</v>
       </c>
       <c r="D39" t="str">
         <v/>
@@ -1425,65 +1425,65 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>[SUPPORT] Обслуживание</v>
+        <v>[FINANCE] Оплата и финансы</v>
       </c>
       <c r="B40" t="str">
-        <v>[TARIF] Смена тарифного плана</v>
+        <v>[BILLING] Формирование счета</v>
       </c>
       <c r="C40" t="str">
-        <v>[MOBILE] Я, как клиент, хочу сменить мобильный тарифный план</v>
+        <v>ТБД</v>
       </c>
       <c r="D40" t="str">
-        <v>2.5 [FINAL] Я как клиент хочу перейти на тарифный план UP в мобильном приложении</v>
-      </c>
-      <c r="E40">
-        <v>130</v>
-      </c>
-      <c r="F40">
-        <v>25</v>
-      </c>
-      <c r="G40">
-        <v>16</v>
-      </c>
-      <c r="H40">
-        <v>15</v>
+        <v/>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>[SUPPORT] Обслуживание</v>
+        <v>[FINANCE] Оплата и финансы</v>
       </c>
       <c r="B41" t="str">
-        <v>[TARIF] Смена тарифного плана</v>
+        <v>[PAYMETHOD] Управление методами оплаты</v>
       </c>
       <c r="C41" t="str">
-        <v>[MOBILE] Я, как клиент, хочу сменить мобильный тарифный план</v>
+        <v>[CHANGE] Я, как клиент, хочу сменить метод оплаты</v>
       </c>
       <c r="D41" t="str">
-        <v>2.1 Я как клиент перехожу на Тарифны План Up в личном кабинете на сайте</v>
-      </c>
-      <c r="E41">
-        <v>260</v>
-      </c>
-      <c r="F41">
-        <v>119</v>
-      </c>
-      <c r="G41">
-        <v>15</v>
-      </c>
-      <c r="H41">
-        <v>13</v>
+        <v/>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>[SUPPORT] Обслуживание</v>
+        <v>[FINANCE] Оплата и финансы</v>
       </c>
       <c r="B42" t="str">
-        <v>[TARIF] Смена тарифного плана</v>
+        <v>[DETAILS] Просмотр детализации и истории платежей</v>
       </c>
       <c r="C42" t="str">
-        <v>[FIX] Я, как клиент, хочу сменить тарифный план на домашний интернет и ТВ</v>
+        <v>[PAY-APP] Я, как клиент, хочу получить историю поплнений через мобильное приложение</v>
       </c>
       <c r="D42" t="str">
         <v/>
@@ -1503,13 +1503,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>[SUPPORT] Обслуживание</v>
+        <v>[FINANCE] Оплата и финансы</v>
       </c>
       <c r="B43" t="str">
-        <v>[TARIF] Смена тарифного плана</v>
+        <v>[DETAILS] Просмотр детализации и истории платежей</v>
       </c>
       <c r="C43" t="str">
-        <v>[CONVERGENT] Я, как клиент, хочу поменять условия конвергентного тарифного плана</v>
+        <v>[PAY-ELK] Я, как клиент, хочу получить историю пополнений через ЕЛК</v>
       </c>
       <c r="D43" t="str">
         <v/>
@@ -1529,39 +1529,39 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>[SUPPORT] Обслуживание</v>
+        <v>[FINANCE] Оплата и финансы</v>
       </c>
       <c r="B44" t="str">
-        <v>[SERVICE] Подключение/отключение услуг</v>
+        <v>[DETAILS] Просмотр детализации и истории платежей</v>
       </c>
       <c r="C44" t="str">
-        <v>[MOBILE] Я, как клиент, хочу подключить или отключить услугу на мобильном тарифном плане</v>
+        <v>[APP] Я, как клиент, хочу получить детализацию через мобильное приложение</v>
       </c>
       <c r="D44" t="str">
-        <v/>
-      </c>
-      <c r="E44" t="str">
-        <v/>
-      </c>
-      <c r="F44" t="str">
-        <v/>
-      </c>
-      <c r="G44" t="str">
-        <v/>
-      </c>
-      <c r="H44" t="str">
-        <v/>
+        <v>Я, как клиент, хочу получить Детализацию через мобильное приложение</v>
+      </c>
+      <c r="E44">
+        <v>35</v>
+      </c>
+      <c r="F44">
+        <v>14</v>
+      </c>
+      <c r="G44">
+        <v>10</v>
+      </c>
+      <c r="H44">
+        <v>9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>[SUPPORT] Обслуживание</v>
+        <v>[FINANCE] Оплата и финансы</v>
       </c>
       <c r="B45" t="str">
-        <v>[SERVICE] Подключение/отключение услуг</v>
+        <v>[DETAILS] Просмотр детализации и истории платежей</v>
       </c>
       <c r="C45" t="str">
-        <v>[FIX] Я, как клиент, хочу подключить или отключить услугу фиксированной связи</v>
+        <v>[ELK] Я, как клиент, хочу получить детализацию начислений через ЕЛК</v>
       </c>
       <c r="D45" t="str">
         <v/>
@@ -1581,13 +1581,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>[SUPPORT] Обслуживание</v>
+        <v>[FINANCE] Оплата и финансы</v>
       </c>
       <c r="B46" t="str">
-        <v>[SERVICE] Подключение/отключение услуг</v>
+        <v>[ERR] Ошибочный платеж</v>
       </c>
       <c r="C46" t="str">
-        <v>[CONVERGENT] Я, как клиент, хочу поменять условия конвергентного тарифного плана</v>
+        <v>[RETURN] Я, как клиент, хочу вернуть ошибочный платеж</v>
       </c>
       <c r="D46" t="str">
         <v/>
@@ -1607,13 +1607,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>[SUPPORT] Обслуживание</v>
+        <v>[FINANCE] Оплата и финансы</v>
       </c>
       <c r="B47" t="str">
-        <v>[FAMALY] Семья в билайн</v>
+        <v>[BALANCE] Управление балансами ЛС</v>
       </c>
       <c r="C47" t="str">
-        <v>[SUBSCRIBE] Я, как клиент, хочу подключить подписку Все для семьи</v>
+        <v>[SMS-INFO] Я, как клиент, хочу получить информацию о балансе через СМС</v>
       </c>
       <c r="D47" t="str">
         <v/>
@@ -1633,13 +1633,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>[SUPPORT] Обслуживание</v>
+        <v>[FINANCE] Оплата и финансы</v>
       </c>
       <c r="B48" t="str">
-        <v>[FAMALY] Семья в билайн</v>
+        <v>[BALANCE] Управление балансами ЛС</v>
       </c>
       <c r="C48" t="str">
-        <v>[INCLUDE] Я, как клиент, хоче подключить близких в в Семью билайн</v>
+        <v>[APP-INFO] Я, как клиент, хочу посмотреть баланс в мобильном приложении</v>
       </c>
       <c r="D48" t="str">
         <v/>
@@ -1659,13 +1659,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>[SUPPORT] Обслуживание</v>
+        <v>[FINANCE] Оплата и финансы</v>
       </c>
       <c r="B49" t="str">
-        <v>[FAMALY] Семья в билайн</v>
+        <v>[BALANCE] Управление балансами ЛС</v>
       </c>
       <c r="C49" t="str">
-        <v>[SHARE] Я, как клиент, хочу поделиться тарифом с близкими</v>
+        <v>[LK-INFO] Я, как клиент, хочу посмотреть баланс в ЕЛК</v>
       </c>
       <c r="D49" t="str">
         <v/>
@@ -1685,13 +1685,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>[SUPPORT] Обслуживание</v>
+        <v>[FINANCE] Оплата и финансы</v>
       </c>
       <c r="B50" t="str">
-        <v>[FAMALY] Семья в билайн</v>
+        <v>[BALANCE] Управление балансами ЛС</v>
       </c>
       <c r="C50" t="str">
-        <v>[INFO] Я, как клиент, хочу получить информацию о балансах близких</v>
+        <v>[EXTRA] Я, как клиент, хочу пополнить дополнительный баланс для мобильной оплаты</v>
       </c>
       <c r="D50" t="str">
         <v/>
@@ -1711,13 +1711,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>[SUPPORT] Обслуживание</v>
+        <v>[FINANCE] Оплата и финансы</v>
       </c>
       <c r="B51" t="str">
-        <v>[ACCOUNT] Управление аккаунтами</v>
+        <v>[BALANCE] Управление балансами ЛС</v>
       </c>
       <c r="C51" t="str">
-        <v>[ELK] Я, как клиент, хочу добавить аккаунт для управления в ЕЛК</v>
+        <v>[AUTO] Я, как клиент, хочу настроить автоплатеж</v>
       </c>
       <c r="D51" t="str">
         <v/>
@@ -1737,13 +1737,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>[SUPPORT] Обслуживание</v>
+        <v>[FINANCE] Оплата и финансы</v>
       </c>
       <c r="B52" t="str">
-        <v>[ACCOUNT] Управление аккаунтами</v>
+        <v>[BALANCE] Управление балансами ЛС</v>
       </c>
       <c r="C52" t="str">
-        <v>[APP] Я, как клиент, хчоу добавить аккаунт для управления в мобильном приложении</v>
+        <v>[SMS] Я, как клиент, хочу пополнить баланс с другого мобильного ЛС через СМС</v>
       </c>
       <c r="D52" t="str">
         <v/>
@@ -1763,13 +1763,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>[SUPPORT] Обслуживание</v>
+        <v>[FINANCE] Оплата и финансы</v>
       </c>
       <c r="B53" t="str">
-        <v>[DEVICE] Замена SIM и номера</v>
+        <v>[BALANCE] Управление балансами ЛС</v>
       </c>
       <c r="C53" t="str">
-        <v>[MSISDN] Я,  как клиент, хочу поменять номер телефона</v>
+        <v>[PHONE] Я, как клиент, хочу пополнить баланс с другого мобильного ЛС на сайте</v>
       </c>
       <c r="D53" t="str">
         <v/>
@@ -1789,13 +1789,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>[SUPPORT] Обслуживание</v>
+        <v>[FINANCE] Оплата и финансы</v>
       </c>
       <c r="B54" t="str">
-        <v>[DEVICE] Замена SIM и номера</v>
+        <v>[BALANCE] Управление балансами ЛС</v>
       </c>
       <c r="C54" t="str">
-        <v>[SIM] Я,  как  клиент, хочу поменять SIM карту</v>
+        <v>[EVALLET] Я, как клиент, хочу пополнить баланс с электронного кошелька</v>
       </c>
       <c r="D54" t="str">
         <v/>
@@ -1815,13 +1815,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>[SUPPORT] Обслуживание</v>
+        <v>[FINANCE] Оплата и финансы</v>
       </c>
       <c r="B55" t="str">
-        <v>[INFO] Изменение/подтверждение персональных данных</v>
+        <v>[BALANCE] Управление балансами ЛС</v>
       </c>
       <c r="C55" t="str">
-        <v>[ESIA] Я, как клиент, хочу обновить персональные данные через ГОСУСЛУГИ</v>
+        <v>[CASH] Я, как клиент, хочу поплнить баланс наличными в офисе билайн</v>
       </c>
       <c r="D55" t="str">
         <v/>
@@ -1841,13 +1841,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>[SUPPORT] Обслуживание</v>
+        <v>[FINANCE] Оплата и финансы</v>
       </c>
       <c r="B56" t="str">
-        <v>[INFO] Изменение/подтверждение персональных данных</v>
+        <v>[BALANCE] Управление балансами ЛС</v>
       </c>
       <c r="C56" t="str">
-        <v>[OFFICE] Я, как клиент, хочу обновить персональные данные в офисе билайн</v>
+        <v>[TERMINAL] Я, как клиент, хочу пополнить баланс через терминал оплаты</v>
       </c>
       <c r="D56" t="str">
         <v/>
@@ -1867,13 +1867,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>[SUPPORT] Обслуживание</v>
+        <v>[FINANCE] Оплата и финансы</v>
       </c>
       <c r="B57" t="str">
-        <v>[INFO] Изменение/подтверждение персональных данных</v>
+        <v>[BALANCE] Управление балансами ЛС</v>
       </c>
       <c r="C57" t="str">
-        <v>[CONTRACT] я, как клиент изменяю данные по договору/клиенту (изменение ИНН, наименования, КПП, адреса, контактного лица и прочее)</v>
+        <v>[ATM] Я, как клиент, хочу пополнить баланс через банкомат</v>
       </c>
       <c r="D57" t="str">
         <v/>
@@ -1893,13 +1893,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>[SUPPORT] Обслуживание</v>
+        <v>[FINANCE] Оплата и финансы</v>
       </c>
       <c r="B58" t="str">
-        <v>[OWNER] Смена владельца номера</v>
+        <v>[BALANCE] Управление балансами ЛС</v>
       </c>
       <c r="C58" t="str">
-        <v>[INDIVIDUAL] Я, как клиент, хочу переормить мобильный номер другого человека на себя</v>
+        <v>[BANKAPP] Я, как клиент, хочу попонить баланс из банковского приложения</v>
       </c>
       <c r="D58" t="str">
         <v/>
@@ -1919,13 +1919,13 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>[SUPPORT] Обслуживание</v>
+        <v>[FINANCE] Оплата и финансы</v>
       </c>
       <c r="B59" t="str">
-        <v>[OWNER] Смена владельца номера</v>
+        <v>[BALANCE] Управление балансами ЛС</v>
       </c>
       <c r="C59" t="str">
-        <v>[IDENTIFY] Я, как клиент, хочу переформить мобильный номер на себя с альтернативной идентификацией</v>
+        <v>[APP] Я, как клиент, хочу пополнить баланс из мобильного приложения</v>
       </c>
       <c r="D59" t="str">
         <v/>
@@ -1945,13 +1945,13 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>[SUPPORT] Обслуживание</v>
+        <v>[FINANCE] Оплата и финансы</v>
       </c>
       <c r="B60" t="str">
-        <v>[OWNER] Смена владельца номера</v>
+        <v>[BALANCE] Управление балансами ЛС</v>
       </c>
       <c r="C60" t="str">
-        <v>[ORG] Я, как клиент, хочу переформить юрлица номер юр.лица на себя</v>
+        <v>[BEELINE.RU] Я, как клиент, хочу пополнить баланс с сайта beeline.ru</v>
       </c>
       <c r="D60" t="str">
         <v/>
@@ -1971,13 +1971,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>[SUPPORT] Обслуживание</v>
+        <v>[FINANCE] Оплата и финансы</v>
       </c>
       <c r="B61" t="str">
-        <v>[LOCK] Добровольная блокировка разблокировка</v>
+        <v>Доверительный платеж</v>
       </c>
       <c r="C61" t="str">
-        <v>[ADD] Я, как клиент, хочу добровольно заблокировать свой  мобильный номер телефона</v>
+        <v>[TRUST] Я, как клиент, хочу подключить доверительный платеж</v>
       </c>
       <c r="D61" t="str">
         <v/>
@@ -1997,13 +1997,13 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>[SUPPORT] Обслуживание</v>
+        <v>[FINANCE] Оплата и финансы</v>
       </c>
       <c r="B62" t="str">
-        <v>[LOCK] Добровольная блокировка разблокировка</v>
+        <v>[PAY] Оплата с ЛС</v>
       </c>
       <c r="C62" t="str">
-        <v>[REMOVE] Я, как клиент, хочу разблокировать свой мобильный номер телефона</v>
+        <v>[CREDIT] Я, как клиент, хочу погасить кредит с мобильного ЛС</v>
       </c>
       <c r="D62" t="str">
         <v/>
@@ -2023,13 +2023,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>[SUPPORT] Обслуживание</v>
+        <v>[FINANCE] Оплата и финансы</v>
       </c>
       <c r="B63" t="str">
-        <v>[LOCK] Добровольная блокировка разблокировка</v>
+        <v>[PAY] Оплата с ЛС</v>
       </c>
       <c r="C63" t="str">
-        <v>[ADDFIX] Я, как клиент, хочу добровольно заблокировать домашиний интернет</v>
+        <v>[SOCIAL] Я, как клиент, хочу сделать платеж в соц.сетях с мобильного ЛС</v>
       </c>
       <c r="D63" t="str">
         <v/>
@@ -2049,13 +2049,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>[SUPPORT] Обслуживание</v>
+        <v>[FINANCE] Оплата и финансы</v>
       </c>
       <c r="B64" t="str">
-        <v>[LOCK] Добровольная блокировка разблокировка</v>
+        <v>[PAY] Оплата с ЛС</v>
       </c>
       <c r="C64" t="str">
-        <v>[REMOVEFIX] Я, как клиент, хочу разблокировать домашний интернет</v>
+        <v>[SMS] Я, как клиент, хочу оплатить по SMS с мобильного ЛС</v>
       </c>
       <c r="D64" t="str">
         <v/>
@@ -2075,13 +2075,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>[SUPPORT] Обслуживание</v>
+        <v>[FINANCE] Оплата и финансы</v>
       </c>
       <c r="B65" t="str">
-        <v>[PIN] Восстановление PIN\PUK</v>
+        <v>[PAY] Оплата с ЛС</v>
       </c>
       <c r="C65" t="str">
-        <v>[PUK] Я, как клиент, хочу разблокировать SIM и восстановить PIN с использованием PUK кода</v>
+        <v>[TRANSFER] Я, как клиент, хочу сделать перевод с мобильного ЛС</v>
       </c>
       <c r="D65" t="str">
         <v/>
@@ -2101,13 +2101,13 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>[SUPPORT] Обслуживание</v>
+        <v>[FINANCE] Оплата и финансы</v>
       </c>
       <c r="B66" t="str">
-        <v>[PIN] Восстановление PIN\PUK</v>
+        <v>[PAY] Оплата с ЛС</v>
       </c>
       <c r="C66" t="str">
-        <v>[CALL] Я, как клиент, хочу разбокировать SIM и восстановить PIN звонком по телефону</v>
+        <v>[APPSTORE] Я, как клиент, хочу провести оплату в app story/google play через мобильный платеж</v>
       </c>
       <c r="D66" t="str">
         <v/>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>[SUPPORT] Обслуживание</v>
+        <v>[FINANCE] Оплата и финансы</v>
       </c>
       <c r="B67" t="str">
-        <v>[PIN] Восстановление PIN\PUK</v>
+        <v>[PAY] Оплата с ЛС</v>
       </c>
       <c r="C67" t="str">
-        <v>[OFFICE] Я, как клиент, хочу разблокировать SIM и восстановить PIN в офисе билайн</v>
+        <v>[ISHOP] Я, как клиент, хочу провести оплату в интеренете через мобильный платеж</v>
       </c>
       <c r="D67" t="str">
         <v/>
@@ -2153,13 +2153,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>[SUPPORT] Обслуживание</v>
+        <v>[FINANCE] Оплата и финансы</v>
       </c>
       <c r="B68" t="str">
-        <v>[CTE] Сервисное обслуживание АБО (работа с возвратами, браком, ТВП, расхождениями и прочее)</v>
+        <v>[PAY] Оплата с ЛС</v>
       </c>
       <c r="C68" t="str">
-        <v>ТБД</v>
+        <v>[MOBILE] Я, как клиент, хочу провести оплату через мобильный платеж</v>
       </c>
       <c r="D68" t="str">
         <v/>
@@ -2179,39 +2179,39 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>[SUPPORT] Обслуживание</v>
+        <v>[FINANCE] Оплата и финансы</v>
       </c>
       <c r="B69" t="str">
-        <v>[IMPROVE-MOBILE] Регламент "Улучшение покрытия мобильной сети для абонентов В2В"</v>
+        <v>[PAY] Оплата с ЛС</v>
       </c>
       <c r="C69" t="str">
-        <v>ТБД</v>
+        <v>[FEE] Я, как клиент, хочу оплатить абоненскую плату с баланса ЛС</v>
       </c>
       <c r="D69" t="str">
-        <v/>
-      </c>
-      <c r="E69" t="str">
-        <v/>
-      </c>
-      <c r="F69" t="str">
-        <v/>
-      </c>
-      <c r="G69" t="str">
-        <v/>
-      </c>
-      <c r="H69" t="str">
-        <v/>
+        <v>Я, как клиент, хочу оплатить абонентскую плату с баланса ЛС</v>
+      </c>
+      <c r="E69">
+        <v>16</v>
+      </c>
+      <c r="F69">
+        <v>8</v>
+      </c>
+      <c r="G69">
+        <v>6</v>
+      </c>
+      <c r="H69">
+        <v>5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>[SUPPORT] Обслуживание</v>
+        <v>[CUST] Управление клиентами</v>
       </c>
       <c r="B70" t="str">
-        <v>[TRANSFER] Переезд</v>
+        <v>[GOVERNANCE] Работа с государственными клиентами</v>
       </c>
       <c r="C70" t="str">
-        <v>[FIX] Я, как клиент, хочу перенести домашний интернет на новую квартиру</v>
+        <v/>
       </c>
       <c r="D70" t="str">
         <v/>
@@ -2231,13 +2231,13 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>[FINANCE] Оплата и финансы</v>
+        <v>[CUST] Управление клиентами</v>
       </c>
       <c r="B71" t="str">
-        <v>[PAY] Оплата с ЛС</v>
+        <v>Создание(изменение) Группы Компании/Добавление Компании в ГК</v>
       </c>
       <c r="C71" t="str">
-        <v>[FEE] Я, как клиент, хочу оплатить абоненскую плату с баланса ЛС</v>
+        <v/>
       </c>
       <c r="D71" t="str">
         <v/>
@@ -2257,13 +2257,13 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>[FINANCE] Оплата и финансы</v>
+        <v>[CUST] Управление клиентами</v>
       </c>
       <c r="B72" t="str">
-        <v>[PAY] Оплата с ЛС</v>
+        <v>Персональные менеджеры</v>
       </c>
       <c r="C72" t="str">
-        <v>[MOBILE] Я, как клиент, хочу провести оплату через мобильный платеж</v>
+        <v>Закрепление/открепление/изменение Личного Оператора</v>
       </c>
       <c r="D72" t="str">
         <v/>
@@ -2283,13 +2283,13 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>[FINANCE] Оплата и финансы</v>
+        <v>[AGREEMENT] Управление контрактами и условиями договоров</v>
       </c>
       <c r="B73" t="str">
-        <v>[PAY] Оплата с ЛС</v>
+        <v>[SLA] Предоставление уровня обслуживания (АТ,SM в том числе)</v>
       </c>
       <c r="C73" t="str">
-        <v>[ISHOP] Я, как клиент, хочу провести оплату в интеренете через мобильный платеж</v>
+        <v/>
       </c>
       <c r="D73" t="str">
         <v/>
@@ -2309,13 +2309,13 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>[FINANCE] Оплата и финансы</v>
+        <v>[AGREEMENT] Управление контрактами и условиями договоров</v>
       </c>
       <c r="B74" t="str">
-        <v>[PAY] Оплата с ЛС</v>
+        <v>Работа с нерезидентами</v>
       </c>
       <c r="C74" t="str">
-        <v>[APPSTORE] Я, как клиент, хочу провести оплату в app story/google play через мобильный платеж</v>
+        <v/>
       </c>
       <c r="D74" t="str">
         <v/>
@@ -2335,13 +2335,13 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>[FINANCE] Оплата и финансы</v>
+        <v>[AGREEMENT] Управление контрактами и условиями договоров</v>
       </c>
       <c r="B75" t="str">
-        <v>[PAY] Оплата с ЛС</v>
+        <v>[ARCHIVE] Архивация клиентской документации</v>
       </c>
       <c r="C75" t="str">
-        <v>[TRANSFER] Я, как клиент, хочу сделать перевод с мобильного ЛС</v>
+        <v/>
       </c>
       <c r="D75" t="str">
         <v/>
@@ -2361,13 +2361,13 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>[FINANCE] Оплата и финансы</v>
+        <v>[AGREEMENT] Управление контрактами и условиями договоров</v>
       </c>
       <c r="B76" t="str">
-        <v>[PAY] Оплата с ЛС</v>
+        <v>ТБД Сохранение/расторжение Клиента</v>
       </c>
       <c r="C76" t="str">
-        <v>[SMS] Я, как клиент, хочу оплатить по SMS с мобильного ЛС</v>
+        <v/>
       </c>
       <c r="D76" t="str">
         <v/>
@@ -2387,13 +2387,13 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>[FINANCE] Оплата и финансы</v>
+        <v>[AGREEMENT] Управление контрактами и условиями договоров</v>
       </c>
       <c r="B77" t="str">
-        <v>[PAY] Оплата с ЛС</v>
+        <v>[PRIVATE] Предоставление непубличных условий клиентам mob</v>
       </c>
       <c r="C77" t="str">
-        <v>[SOCIAL] Я, как клиент, хочу сделать платеж в соц.сетях с мобильного ЛС</v>
+        <v>ТБД</v>
       </c>
       <c r="D77" t="str">
         <v/>
@@ -2413,13 +2413,13 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>[FINANCE] Оплата и финансы</v>
+        <v>[LOYALTY] Управление лояльностью</v>
       </c>
       <c r="B78" t="str">
-        <v>[PAY] Оплата с ЛС</v>
+        <v>ТБД</v>
       </c>
       <c r="C78" t="str">
-        <v>[CREDIT] Я, как клиент, хочу погасить кредит с мобильного ЛС</v>
+        <v/>
       </c>
       <c r="D78" t="str">
         <v/>
@@ -2439,13 +2439,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>[FINANCE] Оплата и финансы</v>
+        <v>[PARTNER] Управление партнерами</v>
       </c>
       <c r="B79" t="str">
-        <v>Доверительный платеж</v>
+        <v>[TENDER] Процедура по работе с тендерами</v>
       </c>
       <c r="C79" t="str">
-        <v>[TRUST] Я, как клиент, хочу подключить доверительный платеж</v>
+        <v/>
       </c>
       <c r="D79" t="str">
         <v/>
@@ -2465,13 +2465,13 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>[FINANCE] Оплата и финансы</v>
+        <v>[PARTNER] Управление партнерами</v>
       </c>
       <c r="B80" t="str">
-        <v>[BALANCE] Управление балансами ЛС</v>
+        <v>[AGENT] Процедура по работе с Агентами</v>
       </c>
       <c r="C80" t="str">
-        <v>[BEELINE.RU] Я, как клиент, хочу пополнить баланс с сайта beeline.ru</v>
+        <v/>
       </c>
       <c r="D80" t="str">
         <v/>
@@ -2491,13 +2491,13 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>[FINANCE] Оплата и финансы</v>
+        <v>[SALE] Продажи</v>
       </c>
       <c r="B81" t="str">
-        <v>[BALANCE] Управление балансами ЛС</v>
+        <v>[PLAY] Игры и развлечения</v>
       </c>
       <c r="C81" t="str">
-        <v>[APP] Я, как клиент, хочу пополнить баланс из мобильного приложения</v>
+        <v>[] Я, как клиент покупаю развлекательные подписки</v>
       </c>
       <c r="D81" t="str">
         <v/>
@@ -2517,13 +2517,13 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>[FINANCE] Оплата и финансы</v>
+        <v>[SALE] Продажи</v>
       </c>
       <c r="B82" t="str">
-        <v>[BALANCE] Управление балансами ЛС</v>
+        <v>[PLAY] Игры и развлечения</v>
       </c>
       <c r="C82" t="str">
-        <v>[BANKAPP] Я, как клиент, хочу попонить баланс из банковского приложения</v>
+        <v>[CLOUD] Я, как клиент, хочу купить подписку на облако билайн</v>
       </c>
       <c r="D82" t="str">
         <v/>
@@ -2543,13 +2543,13 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>[FINANCE] Оплата и финансы</v>
+        <v>[SALE] Продажи</v>
       </c>
       <c r="B83" t="str">
-        <v>[BALANCE] Управление балансами ЛС</v>
+        <v>[PLAY] Игры и развлечения</v>
       </c>
       <c r="C83" t="str">
-        <v>[ATM] Я, как клиент, хочу пополнить баланс через банкомат</v>
+        <v>[BOOKS] Я, как клиент, хочу купить подписку на билайн книги</v>
       </c>
       <c r="D83" t="str">
         <v/>
@@ -2569,13 +2569,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>[FINANCE] Оплата и финансы</v>
+        <v>[SALE] Продажи</v>
       </c>
       <c r="B84" t="str">
-        <v>[BALANCE] Управление балансами ЛС</v>
+        <v>[RETAIL] Розничные продажи</v>
       </c>
       <c r="C84" t="str">
-        <v>[TERMINAL] Я, как клиент, хочу пополнить баланс через терминал оплаты</v>
+        <v>[CANCEL] Я, как клиент, отменяю заказ</v>
       </c>
       <c r="D84" t="str">
         <v/>
@@ -2595,13 +2595,13 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>[FINANCE] Оплата и финансы</v>
+        <v>[SALE] Продажи</v>
       </c>
       <c r="B85" t="str">
-        <v>[BALANCE] Управление балансами ЛС</v>
+        <v>[RETAIL] Розничные продажи</v>
       </c>
       <c r="C85" t="str">
-        <v>[CASH] Я, как клиент, хочу поплнить баланс наличными в офисе билайн</v>
+        <v>[RETURNS] Я, как клиент, хочу сделать возврат товара</v>
       </c>
       <c r="D85" t="str">
         <v/>
@@ -2621,13 +2621,13 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>[FINANCE] Оплата и финансы</v>
+        <v>[SALE] Продажи</v>
       </c>
       <c r="B86" t="str">
-        <v>[BALANCE] Управление балансами ЛС</v>
+        <v>[RETAIL] Розничные продажи</v>
       </c>
       <c r="C86" t="str">
-        <v>[EVALLET] Я, как клиент, хочу пополнить баланс с электронного кошелька</v>
+        <v>[DIGITAL] Я, как клиент, хочу купить цифровой продукт</v>
       </c>
       <c r="D86" t="str">
         <v/>
@@ -2647,13 +2647,13 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>[FINANCE] Оплата и финансы</v>
+        <v>[SALE] Продажи</v>
       </c>
       <c r="B87" t="str">
-        <v>[BALANCE] Управление балансами ЛС</v>
+        <v>[RETAIL] Розничные продажи</v>
       </c>
       <c r="C87" t="str">
-        <v>[PHONE] Я, как клиент, хочу пополнить баланс с другого мобильного ЛС на сайте</v>
+        <v>Я, как клиент, хочу купить товар в интернет-магазине</v>
       </c>
       <c r="D87" t="str">
         <v/>
@@ -2673,13 +2673,13 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>[FINANCE] Оплата и финансы</v>
+        <v>[SALE] Продажи</v>
       </c>
       <c r="B88" t="str">
-        <v>[BALANCE] Управление балансами ЛС</v>
+        <v>[RETAIL] Розничные продажи</v>
       </c>
       <c r="C88" t="str">
-        <v>[SMS] Я, как клиент, хочу пополнить баланс с другого мобильного ЛС через СМС</v>
+        <v>[TRADEIN] Я, как клиент, хочу купить товар в trade-in</v>
       </c>
       <c r="D88" t="str">
         <v/>
@@ -2699,13 +2699,13 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>[FINANCE] Оплата и финансы</v>
+        <v>[SALE] Продажи</v>
       </c>
       <c r="B89" t="str">
-        <v>[BALANCE] Управление балансами ЛС</v>
+        <v>[RETAIL] Розничные продажи</v>
       </c>
       <c r="C89" t="str">
-        <v>[AUTO] Я, как клиент, хочу настроить автоплатеж</v>
+        <v>[GOODS] Я, как клиент, хочу купить товар</v>
       </c>
       <c r="D89" t="str">
         <v/>
@@ -2725,13 +2725,13 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>[FINANCE] Оплата и финансы</v>
+        <v>[SALE] Продажи</v>
       </c>
       <c r="B90" t="str">
-        <v>[BALANCE] Управление балансами ЛС</v>
+        <v>[CTE] Продажа и аренда фикс.оборудования</v>
       </c>
       <c r="C90" t="str">
-        <v>[EXTRA] Я, как клиент, хочу пополнить дополнительный баланс для мобильной оплаты</v>
+        <v>[RENT] Я, как клиент, хочу взять в аренту оборудование для домашнего интернета и ТВ</v>
       </c>
       <c r="D90" t="str">
         <v/>
@@ -2751,39 +2751,39 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>[FINANCE] Оплата и финансы</v>
+        <v>[SALE] Продажи</v>
       </c>
       <c r="B91" t="str">
-        <v>[BALANCE] Управление балансами ЛС</v>
+        <v>[CTE] Продажа и аренда фикс.оборудования</v>
       </c>
       <c r="C91" t="str">
-        <v>[LK-INFO] Я, как клиент, хочу посмотреть баланс в ЕЛК</v>
+        <v>[SALE] Я, как клиент, покупаю оборудование для домашнего интернета и ТВ</v>
       </c>
       <c r="D91" t="str">
-        <v/>
-      </c>
-      <c r="E91" t="str">
-        <v/>
-      </c>
-      <c r="F91" t="str">
-        <v/>
-      </c>
-      <c r="G91" t="str">
-        <v/>
-      </c>
-      <c r="H91" t="str">
-        <v/>
+        <v>Я, как клиент, хочу купить оборудования для домашнего интернета xDSL (OLD с коммутаторами)</v>
+      </c>
+      <c r="E91">
+        <v>14</v>
+      </c>
+      <c r="F91">
+        <v>3</v>
+      </c>
+      <c r="G91">
+        <v>2</v>
+      </c>
+      <c r="H91">
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>[FINANCE] Оплата и финансы</v>
+        <v>[SALE] Продажи</v>
       </c>
       <c r="B92" t="str">
-        <v>[BALANCE] Управление балансами ЛС</v>
+        <v>[CTE] Продажа и аренда фикс.оборудования</v>
       </c>
       <c r="C92" t="str">
-        <v>[APP-INFO] Я, как клиент, хочу посмотреть баланс в мобильном приложении</v>
+        <v>[RETURNS] Я, как клиент, возвращаю купленное оборудование</v>
       </c>
       <c r="D92" t="str">
         <v/>
@@ -2803,13 +2803,13 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>[FINANCE] Оплата и финансы</v>
+        <v>[SALE] Продажи</v>
       </c>
       <c r="B93" t="str">
-        <v>[BALANCE] Управление балансами ЛС</v>
+        <v>[CONVERGENT] Продажа конвергентных продуктов</v>
       </c>
       <c r="C93" t="str">
-        <v>[SMS-INFO] Я, как клиент, хочу получить информацию о балансе через СМС</v>
+        <v>[MNP] Я, как клиент, хочу подключить домашний интернет, ТВ билайн и перейти по MNP с сохранением своего номера</v>
       </c>
       <c r="D93" t="str">
         <v/>
@@ -2829,13 +2829,13 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>[FINANCE] Оплата и финансы</v>
+        <v>[SALE] Продажи</v>
       </c>
       <c r="B94" t="str">
-        <v>[ERR] Ошибочный платеж</v>
+        <v>[CONVERGENT] Продажа конвергентных продуктов</v>
       </c>
       <c r="C94" t="str">
-        <v>[RETURN] Я, как клиент, хочу вернуть ошибочный платеж</v>
+        <v>[NEWESIM] Я, как клиент, хочу подключить домашний интернет, ТВ билайн и и купить eSIM</v>
       </c>
       <c r="D94" t="str">
         <v/>
@@ -2855,13 +2855,13 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>[FINANCE] Оплата и финансы</v>
+        <v>[SALE] Продажи</v>
       </c>
       <c r="B95" t="str">
-        <v>[DETAILS] Просмотр детализации и истории платежей</v>
+        <v>[CONVERGENT] Продажа конвергентных продуктов</v>
       </c>
       <c r="C95" t="str">
-        <v>[ELK] Я, как клиент, хочу получить детализацию начислений через ЕЛК</v>
+        <v>[PACKAGE] Я, как клиент, хочу подключить домашний интернет, ТВ билайн и сменить тариф на существующем номере</v>
       </c>
       <c r="D95" t="str">
         <v/>
@@ -2881,39 +2881,39 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>[FINANCE] Оплата и финансы</v>
+        <v>[SALE] Продажи</v>
       </c>
       <c r="B96" t="str">
-        <v>[DETAILS] Просмотр детализации и истории платежей</v>
+        <v>[CONVERGENT] Продажа конвергентных продуктов</v>
       </c>
       <c r="C96" t="str">
-        <v>[APP] Я, как клиент, хочу получить детализацию через мобильное приложение</v>
+        <v>[NEWSIM] Я, как клиент, хочу подключить домашний интернет, ТВ билайн и купить новую SIM</v>
       </c>
       <c r="D96" t="str">
-        <v/>
-      </c>
-      <c r="E96" t="str">
-        <v/>
-      </c>
-      <c r="F96" t="str">
-        <v/>
-      </c>
-      <c r="G96" t="str">
-        <v/>
-      </c>
-      <c r="H96" t="str">
-        <v/>
+        <v>Я, как клиент, хочу подключить домашний интернет, ТВ билайн и купить новую SIM</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>[FINANCE] Оплата и финансы</v>
+        <v>[SALE] Продажи</v>
       </c>
       <c r="B97" t="str">
-        <v>[DETAILS] Просмотр детализации и истории платежей</v>
+        <v>[CONNECT] Продажа услуг связи</v>
       </c>
       <c r="C97" t="str">
-        <v>[PAY-ELK] Я, как клиент, хочу получить историю пополнений через ЕЛК</v>
+        <v>[RESTORE] Я, как клиент, хочу восстановить свой номер телефона и купить мобильную связь билайн</v>
       </c>
       <c r="D97" t="str">
         <v/>
@@ -2933,39 +2933,39 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>[FINANCE] Оплата и финансы</v>
+        <v>[SALE] Продажи</v>
       </c>
       <c r="B98" t="str">
-        <v>[DETAILS] Просмотр детализации и истории платежей</v>
+        <v>[CONNECT] Продажа услуг связи</v>
       </c>
       <c r="C98" t="str">
-        <v>[PAY-APP] Я, как клиент, хочу получить историю поплнений через мобильное приложение</v>
+        <v>[FIX] Я, как клиент, хочу купить домашний интернет и ТВ</v>
       </c>
       <c r="D98" t="str">
-        <v/>
-      </c>
-      <c r="E98" t="str">
-        <v/>
-      </c>
-      <c r="F98" t="str">
-        <v/>
-      </c>
-      <c r="G98" t="str">
-        <v/>
-      </c>
-      <c r="H98" t="str">
-        <v/>
+        <v>Я, как Клиент, покупаю услугу домашний интернет xDSL</v>
+      </c>
+      <c r="E98">
+        <v>13</v>
+      </c>
+      <c r="F98">
+        <v>1</v>
+      </c>
+      <c r="G98">
+        <v>3</v>
+      </c>
+      <c r="H98">
+        <v>2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>[FINANCE] Оплата и финансы</v>
+        <v>[SALE] Продажи</v>
       </c>
       <c r="B99" t="str">
-        <v>[PAYMETHOD] Управление методами оплаты</v>
+        <v>[CONNECT] Продажа услуг связи</v>
       </c>
       <c r="C99" t="str">
-        <v>[CHANGE] Я, как клиент, хочу сменить метод оплаты</v>
+        <v>[MNP] Я, как клиент, хочу перейти в билайн с сохранением номера</v>
       </c>
       <c r="D99" t="str">
         <v/>
@@ -2985,13 +2985,13 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>[FINANCE] Оплата и финансы</v>
+        <v>[SALE] Продажи</v>
       </c>
       <c r="B100" t="str">
-        <v>[BILLING] Формирование счета</v>
+        <v>[CONNECT] Продажа услуг связи</v>
       </c>
       <c r="C100" t="str">
-        <v>ТБД</v>
+        <v>[ESIM] Я, как клиент, хочу купить eSIM</v>
       </c>
       <c r="D100" t="str">
         <v/>
@@ -3011,13 +3011,13 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>[FINANCE] Оплата и финансы</v>
+        <v>[SALE] Продажи</v>
       </c>
       <c r="B101" t="str">
-        <v>[CORRECTION]</v>
+        <v>[CONNECT] Продажа услуг связи</v>
       </c>
       <c r="C101" t="str">
-        <v>Предоставление разовых корректировок</v>
+        <v>[NUMBER] Я, как клиент, хочу купить красивый номер на существующую СИМ карту</v>
       </c>
       <c r="D101" t="str">
         <v/>
@@ -3037,13 +3037,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>[FINANCE] Оплата и финансы</v>
+        <v>[SALE] Продажи</v>
       </c>
       <c r="B102" t="str">
-        <v>[DELIVERY] Печать и доставка счета</v>
+        <v>[CONNECT] Продажа услуг связи</v>
       </c>
       <c r="C102" t="str">
-        <v>ТБД</v>
+        <v>Я, как клиент покупаю новую сим-карту с красивым номером</v>
       </c>
       <c r="D102" t="str">
         <v/>
@@ -3063,13 +3063,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>[REQUEST] Обращения</v>
+        <v>[SALE] Продажи</v>
       </c>
       <c r="B103" t="str">
-        <v>[INFO] Консультации</v>
+        <v>[CONNECT] Продажа услуг связи</v>
       </c>
       <c r="C103" t="str">
-        <v>ТБД</v>
+        <v>[SIM] Я, как клиент, покупаю SIM новую карту</v>
       </c>
       <c r="D103" t="str">
         <v/>
@@ -3089,167 +3089,615 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>[REQUEST] Обращения</v>
+        <v>[SALE] Продажи</v>
       </c>
       <c r="B104" t="str">
-        <v>[CLAIMS] Претензии</v>
+        <v>[CONNECT] Продажа услуг связи</v>
       </c>
       <c r="C104" t="str">
-        <v>ТБД</v>
+        <v>[FIX] Я, как клиент подключаю или отключаю услугу фиксированной связи</v>
       </c>
       <c r="D104" t="str">
-        <v/>
-      </c>
-      <c r="E104" t="str">
-        <v/>
-      </c>
-      <c r="F104" t="str">
-        <v/>
-      </c>
-      <c r="G104" t="str">
-        <v/>
-      </c>
-      <c r="H104" t="str">
-        <v/>
+        <v>Я, как Клиент, покупаю услуги домашней телефонии</v>
+      </c>
+      <c r="E104">
+        <v>15</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <v>2</v>
+      </c>
+      <c r="H104">
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>[LOYALTY] Управление лояльностью</v>
+        <v>[SALE] Продажи</v>
       </c>
       <c r="B105" t="str">
-        <v>ТБД</v>
+        <v>[CONNECT] Продажа услуг связи</v>
       </c>
       <c r="C105" t="str">
-        <v/>
+        <v xml:space="preserve">2.1 Я как клиент перехожу на тарифный план UP в личном кабинете на сайте </v>
       </c>
       <c r="D105" t="str">
-        <v/>
-      </c>
-      <c r="E105" t="str">
-        <v/>
-      </c>
-      <c r="F105" t="str">
-        <v/>
-      </c>
-      <c r="G105" t="str">
-        <v/>
-      </c>
-      <c r="H105" t="str">
-        <v/>
+        <v>2.1.2 Я как клиент хочу ознакомиться с доступными для перехода тарифными планами в личном кабинете на сайте</v>
+      </c>
+      <c r="E105">
+        <v>20</v>
+      </c>
+      <c r="F105">
+        <v>1</v>
+      </c>
+      <c r="G105">
+        <v>5</v>
+      </c>
+      <c r="H105">
+        <v>4</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>[PRODUCT] Управление продуктовыми каталогом</v>
+        <v>[SALE] Продажи</v>
       </c>
       <c r="B106" t="str">
-        <v>ТБД</v>
+        <v>[CONNECT] Продажа услуг связи</v>
       </c>
       <c r="C106" t="str">
-        <v/>
+        <v xml:space="preserve">2.1 Я как клиент перехожу на тарифный план UP в личном кабинете на сайте </v>
       </c>
       <c r="D106" t="str">
-        <v/>
-      </c>
-      <c r="E106" t="str">
-        <v/>
-      </c>
-      <c r="F106" t="str">
-        <v/>
-      </c>
-      <c r="G106" t="str">
-        <v/>
-      </c>
-      <c r="H106" t="str">
-        <v/>
+        <v>2.1 Я как клиент перехожу на Тарифный План Up в личном кабинете на сайте</v>
+      </c>
+      <c r="E106">
+        <v>1216</v>
+      </c>
+      <c r="F106">
+        <v>80</v>
+      </c>
+      <c r="G106">
+        <v>27</v>
+      </c>
+      <c r="H106">
+        <v>26</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>[PARTNER] Управление партнерами</v>
+        <v>[SALE] Продажи</v>
       </c>
       <c r="B107" t="str">
-        <v>[AGENT] Процедура по работе с Агентами</v>
+        <v>[CONNECT] Продажа услуг связи</v>
       </c>
       <c r="C107" t="str">
-        <v/>
+        <v xml:space="preserve">2.1 Я как клиент перехожу на тарифный план UP в личном кабинете на сайте </v>
       </c>
       <c r="D107" t="str">
-        <v/>
-      </c>
-      <c r="E107" t="str">
-        <v/>
-      </c>
-      <c r="F107" t="str">
-        <v/>
-      </c>
-      <c r="G107" t="str">
-        <v/>
-      </c>
-      <c r="H107" t="str">
-        <v/>
+        <v>2.1.3 Я как клиент хочу ознакомиться с доступным для перехода тарифным планом Up в личном кабинете на сайте</v>
+      </c>
+      <c r="E107">
+        <v>51</v>
+      </c>
+      <c r="F107">
+        <v>2</v>
+      </c>
+      <c r="G107">
+        <v>11</v>
+      </c>
+      <c r="H107">
+        <v>10</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>[PARTNER] Управление партнерами</v>
+        <v>[SALE] Продажи</v>
       </c>
       <c r="B108" t="str">
-        <v>[TENDER] Процедура по работе с тендерами</v>
+        <v>[CONNECT] Продажа услуг связи</v>
       </c>
       <c r="C108" t="str">
-        <v/>
+        <v xml:space="preserve">2.1 Я как клиент перехожу на тарифный план UP в личном кабинете на сайте </v>
       </c>
       <c r="D108" t="str">
-        <v/>
-      </c>
-      <c r="E108" t="str">
-        <v/>
-      </c>
-      <c r="F108" t="str">
-        <v/>
-      </c>
-      <c r="G108" t="str">
-        <v/>
-      </c>
-      <c r="H108" t="str">
-        <v/>
+        <v>2.1.4 Я как клиент переключаюсь со старого тарифного плана на тариф UP в личном кабинете на сайте</v>
+      </c>
+      <c r="E108">
+        <v>101</v>
+      </c>
+      <c r="F108">
+        <v>17</v>
+      </c>
+      <c r="G108">
+        <v>18</v>
+      </c>
+      <c r="H108">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>[SALE] Продажи</v>
+      </c>
+      <c r="B109" t="str">
+        <v>[CONNECT] Продажа услуг связи</v>
+      </c>
+      <c r="C109" t="str">
+        <v xml:space="preserve">2.1 Я как клиент перехожу на тарифный план UP в личном кабинете на сайте </v>
+      </c>
+      <c r="D109" t="str">
+        <v>2.1.1 Я как мобильный клиент хочу открыть ЕЛК для управления подключенными и доступными услугами</v>
+      </c>
+      <c r="E109">
+        <v>108</v>
+      </c>
+      <c r="F109">
+        <v>0</v>
+      </c>
+      <c r="G109">
+        <v>12</v>
+      </c>
+      <c r="H109">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>[SALE] Продажи</v>
+      </c>
+      <c r="B110" t="str">
+        <v>[CONNECT] Продажа услуг связи</v>
+      </c>
+      <c r="C110" t="str">
+        <v>[FIX] Я, как  клиент, хочу купить интернет для бизнеса</v>
+      </c>
+      <c r="D110" t="str">
+        <v>Я, как клиент B2B, хочу подключить услуги связи - 901</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+      <c r="F110">
+        <v>0</v>
+      </c>
+      <c r="G110">
+        <v>0</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>[SALE] Продажи</v>
+      </c>
+      <c r="B111" t="str">
+        <v>[CONNECT] Продажа услуг связи</v>
+      </c>
+      <c r="C111" t="str">
+        <v>[FIX] Я, как клиент, хочу сменить тарифный план ШПД</v>
+      </c>
+      <c r="D111" t="str">
+        <v>Я, как клиент, хочу сменить ТП ШПД (звонок в CallCenter)</v>
+      </c>
+      <c r="E111">
+        <v>45</v>
+      </c>
+      <c r="F111">
+        <v>11</v>
+      </c>
+      <c r="G111">
+        <v>3</v>
+      </c>
+      <c r="H111">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>[SALE] Продажи</v>
+      </c>
+      <c r="B112" t="str">
+        <v>[CONNECT] Продажа услуг связи</v>
+      </c>
+      <c r="C112" t="str">
+        <v>[FIX] Я, как клиент, хочу сменить тарифный план ШПД</v>
+      </c>
+      <c r="D112" t="str">
+        <v>test sequence</v>
+      </c>
+      <c r="E112">
+        <v>5</v>
+      </c>
+      <c r="F112">
+        <v>0</v>
+      </c>
+      <c r="G112">
+        <v>2</v>
+      </c>
+      <c r="H112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>[USE] Предоставление и тарификация услуг</v>
+      </c>
+      <c r="B113" t="str">
+        <v>[VAS] Предоставление услуг VAS платформ</v>
+      </c>
+      <c r="C113" t="str">
+        <v>[CLOUD] Я, как клиент, хоочу воспользоваться облаком билайн</v>
+      </c>
+      <c r="D113" t="str">
+        <v/>
+      </c>
+      <c r="E113" t="str">
+        <v/>
+      </c>
+      <c r="F113" t="str">
+        <v/>
+      </c>
+      <c r="G113" t="str">
+        <v/>
+      </c>
+      <c r="H113" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>[USE] Предоставление и тарификация услуг</v>
+      </c>
+      <c r="B114" t="str">
+        <v>[VAS] Предоставление услуг VAS платформ</v>
+      </c>
+      <c r="C114" t="str">
+        <v>[BOOKS] Я, как клиент, хочу почитать книги билайн</v>
+      </c>
+      <c r="D114" t="str">
+        <v/>
+      </c>
+      <c r="E114" t="str">
+        <v/>
+      </c>
+      <c r="F114" t="str">
+        <v/>
+      </c>
+      <c r="G114" t="str">
+        <v/>
+      </c>
+      <c r="H114" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>[USE] Предоставление и тарификация услуг</v>
+      </c>
+      <c r="B115" t="str">
+        <v>[VAS] Предоставление услуг VAS платформ</v>
+      </c>
+      <c r="C115" t="str">
+        <v>[MOVIE] Я, как клиент, хочу посмотреть фильм на билайн ТВ</v>
+      </c>
+      <c r="D115" t="str">
+        <v/>
+      </c>
+      <c r="E115" t="str">
+        <v/>
+      </c>
+      <c r="F115" t="str">
+        <v/>
+      </c>
+      <c r="G115" t="str">
+        <v/>
+      </c>
+      <c r="H115" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>[USE] Предоставление и тарификация услуг</v>
+      </c>
+      <c r="B116" t="str">
+        <v>[VAS] Предоставление услуг VAS платформ</v>
+      </c>
+      <c r="C116" t="str">
+        <v>[TV] Я, как клиент, хочу посмотреть TV</v>
+      </c>
+      <c r="D116" t="str">
+        <v/>
+      </c>
+      <c r="E116" t="str">
+        <v/>
+      </c>
+      <c r="F116" t="str">
+        <v/>
+      </c>
+      <c r="G116" t="str">
+        <v/>
+      </c>
+      <c r="H116" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>[USE] Предоставление и тарификация услуг</v>
+      </c>
+      <c r="B117" t="str">
+        <v>[CONNECT] Предоставление услуг связи</v>
+      </c>
+      <c r="C117" t="str">
+        <v>[INETFIX] Я, как клиент, хочу воспользоваться домашним интернетом</v>
+      </c>
+      <c r="D117" t="str">
+        <v/>
+      </c>
+      <c r="E117" t="str">
+        <v/>
+      </c>
+      <c r="F117" t="str">
+        <v/>
+      </c>
+      <c r="G117" t="str">
+        <v/>
+      </c>
+      <c r="H117" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>[USE] Предоставление и тарификация услуг</v>
+      </c>
+      <c r="B118" t="str">
+        <v>[CONNECT] Предоставление услуг связи</v>
+      </c>
+      <c r="C118" t="str">
+        <v>[INETMOBILE] Я, как клиент, хочу воспользоваться мобильным интернетом</v>
+      </c>
+      <c r="D118" t="str">
+        <v/>
+      </c>
+      <c r="E118" t="str">
+        <v/>
+      </c>
+      <c r="F118" t="str">
+        <v/>
+      </c>
+      <c r="G118" t="str">
+        <v/>
+      </c>
+      <c r="H118" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>[USE] Предоставление и тарификация услуг</v>
+      </c>
+      <c r="B119" t="str">
+        <v>[CONNECT] Предоставление услуг связи</v>
+      </c>
+      <c r="C119" t="str">
+        <v>[SMS] Я, как клиент, хочу послать SMS</v>
+      </c>
+      <c r="D119" t="str">
+        <v/>
+      </c>
+      <c r="E119" t="str">
+        <v/>
+      </c>
+      <c r="F119" t="str">
+        <v/>
+      </c>
+      <c r="G119" t="str">
+        <v/>
+      </c>
+      <c r="H119" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>[USE] Предоставление и тарификация услуг</v>
+      </c>
+      <c r="B120" t="str">
+        <v>[CONNECT] Предоставление услуг связи</v>
+      </c>
+      <c r="C120" t="str">
+        <v>[VOICE] Я, как клиент, хочу сделать голосовой звонок</v>
+      </c>
+      <c r="D120" t="str">
+        <v/>
+      </c>
+      <c r="E120" t="str">
+        <v/>
+      </c>
+      <c r="F120" t="str">
+        <v/>
+      </c>
+      <c r="G120" t="str">
+        <v/>
+      </c>
+      <c r="H120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>[USE] Предоставление и тарификация услуг</v>
+      </c>
+      <c r="B121" t="str">
+        <v>[CONNECT] Предоставление услуг связи</v>
+      </c>
+      <c r="C121" t="str">
+        <v>[xDSL]Я, как клиент, хочу воспользоваться домашним интернетом xDSL</v>
+      </c>
+      <c r="D121" t="str">
+        <v>Подключение ADSL/Интернет</v>
+      </c>
+      <c r="E121">
+        <v>3</v>
+      </c>
+      <c r="F121">
+        <v>0</v>
+      </c>
+      <c r="G121">
+        <v>1</v>
+      </c>
+      <c r="H121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>[USE] Предоставление и тарификация услуг</v>
+      </c>
+      <c r="B122" t="str">
+        <v>[CONNECT] Предоставление услуг связи</v>
+      </c>
+      <c r="C122" t="str">
+        <v>[xDSL]Я, как клиент, хочу воспользоваться домашним интернетом xDSL</v>
+      </c>
+      <c r="D122" t="str">
+        <v>Я, как клиент, хочу воспользоваться домашним интернетом xDSL</v>
+      </c>
+      <c r="E122">
+        <v>44</v>
+      </c>
+      <c r="F122">
+        <v>0</v>
+      </c>
+      <c r="G122">
+        <v>2</v>
+      </c>
+      <c r="H122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>[USE] Предоставление и тарификация услуг</v>
+      </c>
+      <c r="B123" t="str">
+        <v>[CONNECT] Предоставление услуг связи</v>
+      </c>
+      <c r="C123" t="str">
+        <v>[xDSL]Я, как клиент, хочу воспользоваться домашним интернетом xDSL</v>
+      </c>
+      <c r="D123" t="str">
+        <v>Old_Я, как клиент, хочу воспользоваться домашним интернетом xDSL</v>
+      </c>
+      <c r="E123">
+        <v>38</v>
+      </c>
+      <c r="F123">
+        <v>6</v>
+      </c>
+      <c r="G123">
+        <v>2</v>
+      </c>
+      <c r="H123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>[TERMINATE] Прекращение обслуживания</v>
+      </c>
+      <c r="B124" t="str">
+        <v>[CONNECT] Отключение услуг связи</v>
+      </c>
+      <c r="C124" t="str">
+        <v>[FIX] Я, как клиент, отключаю услуги фиксированной связи</v>
+      </c>
+      <c r="D124" t="str">
+        <v/>
+      </c>
+      <c r="E124" t="str">
+        <v/>
+      </c>
+      <c r="F124" t="str">
+        <v/>
+      </c>
+      <c r="G124" t="str">
+        <v/>
+      </c>
+      <c r="H124" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>[TERMINATE] Прекращение обслуживания</v>
+      </c>
+      <c r="B125" t="str">
+        <v>[CONVERGENT] Отключение конвергентных продуктов</v>
+      </c>
+      <c r="C125" t="str">
+        <v>Я, как клиент конвергента мобильная связь + ШПД, отказываюсь от продукта мобильной связи</v>
+      </c>
+      <c r="D125" t="str">
+        <v>Я, как клиент конвергента мобильная связь + ШПД, отказываюсь от продукта мобильной связи</v>
+      </c>
+      <c r="E125">
+        <v>0</v>
+      </c>
+      <c r="F125">
+        <v>0</v>
+      </c>
+      <c r="G125">
+        <v>0</v>
+      </c>
+      <c r="H125">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="28">
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B5:B11"/>
-    <mergeCell ref="B12:B15"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="B19:B24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="A5:A26"/>
-    <mergeCell ref="A27:A31"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="B36:B39"/>
-    <mergeCell ref="A32:A39"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="B40:B43"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="B47:B50"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="B61:B64"/>
-    <mergeCell ref="B65:B67"/>
-    <mergeCell ref="A40:A70"/>
-    <mergeCell ref="B71:B78"/>
-    <mergeCell ref="B80:B93"/>
-    <mergeCell ref="B95:B98"/>
-    <mergeCell ref="A71:A102"/>
-    <mergeCell ref="A103:A104"/>
-    <mergeCell ref="A107:A108"/>
+  <mergeCells count="34">
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="A8:A37"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="B47:B60"/>
+    <mergeCell ref="B62:B69"/>
+    <mergeCell ref="A38:A69"/>
+    <mergeCell ref="A70:A72"/>
+    <mergeCell ref="A73:A77"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="B81:B83"/>
+    <mergeCell ref="B84:B89"/>
+    <mergeCell ref="B90:B92"/>
+    <mergeCell ref="B93:B96"/>
+    <mergeCell ref="C105:C109"/>
+    <mergeCell ref="C111:C112"/>
+    <mergeCell ref="B97:B112"/>
+    <mergeCell ref="A81:A112"/>
+    <mergeCell ref="B113:B116"/>
+    <mergeCell ref="C121:C123"/>
+    <mergeCell ref="B117:B123"/>
+    <mergeCell ref="A113:A123"/>
+    <mergeCell ref="A124:A125"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H125"/>
   </ignoredErrors>
 </worksheet>
 </file>